--- a/Zinto_bug_report.xlsx
+++ b/Zinto_bug_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="566">
   <si>
     <t>S no.</t>
   </si>
@@ -55,147 +55,156 @@
     <t>https://prnt.sc/MYmbi4hwhL3i</t>
   </si>
   <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>dashboard</t>
+  </si>
+  <si>
+    <t>header - notification icon</t>
+  </si>
+  <si>
+    <t>click on click on notification icon --&gt; scroll --&gt; it scrolls dashboard page instead of notification page</t>
+  </si>
+  <si>
+    <t>forgot password functionality</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">splash screen </t>
+  </si>
+  <si>
+    <t>footer menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the footer is black in colour it should match with the theme </t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>select delivery address</t>
+  </si>
+  <si>
+    <t>remove cross icon as it is not working and not needed --&gt; location is compulsory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if location is off --&gt; it should show  a pop to enable mobile phone's location </t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">click back </t>
+  </si>
+  <si>
+    <t xml:space="preserve">it should not show exit app pop up instead it should redirect back to home page </t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">add back icon for back navigation in ios and android </t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>logo on header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the logo of login page is mandatory it should be smiley logo provided by client for app </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/feTT0rB2k4v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mobile number field </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill saved phone number --&gt; the colour of the field changes to blue --&gt; it should remain white </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill mobile number --&gt; click open terms or privacy policies --&gt; click back --&gt; the previously filled mobile number should not be removed </t>
+  </si>
+  <si>
+    <t>same in login with email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill unregistered number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if phone number is not registered --&gt; it should show validation that phone number is not registered please sign up </t>
+  </si>
+  <si>
+    <t>imp</t>
+  </si>
+  <si>
+    <t>fill mobile number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click continue --&gt; otp page --&gt; click back --&gt; mobile number should not be removed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sign up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill details </t>
+  </si>
+  <si>
+    <t>click open terms or privacy policies --&gt; click back --&gt; it opens login page instead of sign up page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click open terms or privacy policies --&gt; click back --&gt; the previously filled mobile number should not be removed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">click continue --&gt; otp page --&gt; click back --&gt; name and mobile number is removed and only email is there --&gt; all three fields should be saved </t>
+  </si>
+  <si>
+    <t xml:space="preserve">already registered /login number should not be re- registered --&gt; it should show proper validation </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/-lPUgQ4Fmwk5</t>
+  </si>
+  <si>
+    <t>validation message should be user friendly</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>same email should not be registered again</t>
+  </si>
+  <si>
+    <t>Mobile Number field should accept only valid Indian mobile numbers starting with 6 , 7 ,8 , 9 only</t>
+  </si>
+  <si>
+    <t>sign up /login</t>
+  </si>
+  <si>
+    <t>otp page</t>
+  </si>
+  <si>
+    <t>otp should have timeout functionality set the time limit for otp validation and add a timer there</t>
+  </si>
+  <si>
+    <t>resend otp should work --&gt; the previous otp should not be validate after resend otp</t>
+  </si>
+  <si>
     <t>Resolved</t>
   </si>
   <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>dashboard</t>
-  </si>
-  <si>
-    <t>header - notification icon</t>
-  </si>
-  <si>
-    <t>click on click on notification icon --&gt; scroll --&gt; it scrolls dashboard page instead of notification page</t>
-  </si>
-  <si>
-    <t>forgot password functionality</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">splash screen </t>
-  </si>
-  <si>
-    <t>footer menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the footer is black in colour it should match with the theme </t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>select delivery address</t>
-  </si>
-  <si>
-    <t>remove cross icon as it is not working and not needed --&gt; location is compulsory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if location is off --&gt; it should show  a pop to enable location </t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical </t>
-  </si>
-  <si>
-    <t xml:space="preserve">click back </t>
-  </si>
-  <si>
-    <t xml:space="preserve">it should not show exit app pop up instead it should redirect back to home page </t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">header  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">add back icon for back navigation in ios and android </t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>logo on header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the logo of login page is mandatory it should be smiley logo provided by client for app </t>
-  </si>
-  <si>
-    <t>https://prnt.sc/feTT0rB2k4v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mobile number field </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill saved phone number --&gt; the colour of the field changes to blue --&gt; it should remain white </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill mobile number --&gt; click open terms or privacy policies --&gt; click back --&gt; the previously filled mobile number should not be removed </t>
-  </si>
-  <si>
-    <t>same in login with email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill unregistered number </t>
-  </si>
-  <si>
-    <t xml:space="preserve">if phone number is not registered --&gt; it should show validation that phone number is not registered please sign up </t>
-  </si>
-  <si>
-    <t>imp</t>
-  </si>
-  <si>
-    <t>fill mobile number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click continue --&gt; otp page --&gt; click back --&gt; mobile number should not be removed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sign up </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill details </t>
-  </si>
-  <si>
-    <t>click open terms or privacy policies --&gt; click back --&gt; it opens login page instead of sign up page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click open terms or privacy policies --&gt; click back --&gt; the previously filled mobile number should not be removed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">click continue --&gt; otp page --&gt; click back --&gt; name and mobile number is removed and only email is there --&gt; all three fields should be saved </t>
-  </si>
-  <si>
-    <t xml:space="preserve">already registered /login number should not be re- registered --&gt; it should show proper validation </t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>same email should not be registered again</t>
-  </si>
-  <si>
-    <t>Mobile Number field should accept only valid Indian mobile numbers starting with 6 , 7 ,8 , 9 only</t>
-  </si>
-  <si>
-    <t>sign up /login</t>
-  </si>
-  <si>
-    <t>otp page</t>
-  </si>
-  <si>
-    <t>otp should have timeout functionality set the time limit for otp validation and add a timer there</t>
-  </si>
-  <si>
-    <t>resend otp should work --&gt; the previous otp should not be validate after resend otp</t>
-  </si>
-  <si>
     <t>login with email</t>
   </si>
   <si>
@@ -211,6 +220,9 @@
     <t xml:space="preserve">login with email not working </t>
   </si>
   <si>
+    <t>showing invalid or expired otp</t>
+  </si>
+  <si>
     <t xml:space="preserve">whole app </t>
   </si>
   <si>
@@ -226,6 +238,12 @@
     <t xml:space="preserve">change logo --&gt; add official zinto logo with name beside it </t>
   </si>
   <si>
+    <t>Reopen</t>
+  </si>
+  <si>
+    <t>size of logo should be smaller and add name of the app</t>
+  </si>
+  <si>
     <t xml:space="preserve">all pages </t>
   </si>
   <si>
@@ -253,6 +271,9 @@
     <t>order id should be smaller so that it'll be easy to manage and search orders</t>
   </si>
   <si>
+    <t>in admin done</t>
+  </si>
+  <si>
     <t>there are 2 terms &amp; conditions and privacy policies --&gt; remove one without checkbox</t>
   </si>
   <si>
@@ -268,7 +289,7 @@
     <t>otp</t>
   </si>
   <si>
-    <t xml:space="preserve">deleted user phone number --&gt; it shows too many otp request and other validation but not able to make new account with same phone number </t>
+    <t xml:space="preserve">deleted account's phone number --&gt; it shows too many otp request and other validation but not able to make new account with same phone number </t>
   </si>
   <si>
     <t xml:space="preserve">location </t>
@@ -280,6 +301,9 @@
     <t>https://prnt.sc/d51K7WLpV_6m</t>
   </si>
   <si>
+    <t>still it needs refresh after login</t>
+  </si>
+  <si>
     <t>footer</t>
   </si>
   <si>
@@ -316,6 +340,9 @@
     <t xml:space="preserve">vehicle plate number and driving license number should accept correct format only --&gt; currently they are accepting wrong data </t>
   </si>
   <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
     <t xml:space="preserve">step 3 </t>
   </si>
   <si>
@@ -385,6 +412,9 @@
     <t>edit address --&gt; there should be an option to mark address as default and after marking other address should be unmarked from default --&gt; currently it is selecting first address as default</t>
   </si>
   <si>
+    <t>the default tag still on first address</t>
+  </si>
+  <si>
     <t>header categories</t>
   </si>
   <si>
@@ -445,6 +475,9 @@
     <t>signup</t>
   </si>
   <si>
+    <t xml:space="preserve">taking to user app now </t>
+  </si>
+  <si>
     <t xml:space="preserve">waiting for review </t>
   </si>
   <si>
@@ -478,6 +511,9 @@
     <t>https://prnt.sc/hitbGDWt7Bie</t>
   </si>
   <si>
+    <t xml:space="preserve">now it shows 7 order pending </t>
+  </si>
+  <si>
     <t xml:space="preserve">toast notifications </t>
   </si>
   <si>
@@ -499,6 +535,9 @@
     <t xml:space="preserve">in logo white colour is looking different with background </t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>on clicking back --&gt; should open login page instead of exit app pop up</t>
   </si>
   <si>
@@ -526,7 +565,7 @@
     <t xml:space="preserve">header category </t>
   </si>
   <si>
-    <t>add new header --&gt; apply commission at this level --&gt;fill gst --&gt; it shows not able to make category --&gt; it gst field is empty it'll make category</t>
+    <t>add new header --&gt; apply commission at this level --&gt;fill gst --&gt; if shows not able to make category --&gt; it gst field is empty it'll make category</t>
   </si>
   <si>
     <t xml:space="preserve">edit header --&gt; apply commission at this level --&gt;fill numbers --&gt; 0 should be replaced with filled numbers </t>
@@ -976,7 +1015,7 @@
     <t xml:space="preserve">additem to this order </t>
   </si>
   <si>
-    <t>it should show products whose varients are still in stock</t>
+    <t>it should show products whose variants are still in stock</t>
   </si>
   <si>
     <t>order accepted and order received are same working remove order received tracker and add order packed after order accepted  and them logistics assigned</t>
@@ -1051,14 +1090,632 @@
     <t xml:space="preserve">awaiting customer confirmation is overlapping </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">checkout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">online payment </t>
+  </si>
+  <si>
+    <t>on sliding a slider it gives push notification that order has been placed successfully without completing payment</t>
+  </si>
+  <si>
+    <t>on product card -&gt; store name should be present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shows different amount on new order pop and different in earnings </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sometimes otp is not generating </t>
+  </si>
+  <si>
+    <t xml:space="preserve">otp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">otp should not accept 1234 </t>
+  </si>
+  <si>
+    <t>return order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otp is not generating on return orders for seller </t>
+  </si>
+  <si>
+    <t>recent earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shows settled for all amount that are not yet settled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">order transaction </t>
+  </si>
+  <si>
+    <t>shows 0 for all orders transaction --&gt; should show order amount , type of order (cod , online , wallet) , paid or pending etc</t>
+  </si>
+  <si>
+    <t>rewards and wallet</t>
+  </si>
+  <si>
+    <t>my referral --&gt; button is not visible</t>
+  </si>
+  <si>
+    <t>my referral --&gt; click button --&gt; share on whatsapp --&gt; it shows half page for some time it should not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">my referral --&gt; click button --&gt; share on whatsapp --&gt; it should share play store and app store link </t>
+  </si>
+  <si>
+    <t xml:space="preserve">my referral --&gt; click button --&gt; share on whatsapp --&gt; in login detail add referral code field </t>
+  </si>
+  <si>
+    <t>my referral --&gt; click button --&gt; invite via --&gt; qr code is copying the link instead of qr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">my referral --&gt; click button --&gt; invite via --&gt; mobile should share playstore link </t>
+  </si>
+  <si>
+    <t xml:space="preserve">open any page through clicking a cart --&gt; click back --&gt; it should open previous page instead of profile page </t>
+  </si>
+  <si>
+    <t xml:space="preserve">open any page through clicking a cart --&gt; filter buttons are not visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">recent notification </t>
+  </si>
+  <si>
+    <t>view all should open notification page instead of profile page</t>
+  </si>
+  <si>
+    <t>add store assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">module permission --&gt; needs horizontal scrolling --&gt; it should show everything on same page </t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>view store info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shows - no contact phone --&gt; should show store phone and details </t>
+  </si>
+  <si>
+    <t xml:space="preserve">closed store </t>
+  </si>
+  <si>
+    <t>closed store products should not appear on home page</t>
+  </si>
+  <si>
+    <t>store design</t>
+  </si>
+  <si>
+    <t>the text should be in centre and button should be under text --&gt; fix ui of this page according to phone app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upload logo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">remove is going out of box </t>
+  </si>
+  <si>
+    <t xml:space="preserve">save changes button can be smaller </t>
+  </si>
+  <si>
+    <t>stock management</t>
+  </si>
+  <si>
+    <t>should show variants stocks too and they should also be adjust from this page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in stock filter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">on click in stock filter page refreshes it should not </t>
+  </si>
+  <si>
+    <t>out of stock card</t>
+  </si>
+  <si>
+    <t>out of stock card is smaller than others --&gt; should be same</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> all pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not downloading files everywhere </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre order campaign </t>
+  </si>
+  <si>
+    <t xml:space="preserve">some fields and their titles are not visible </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/D0u9-5gR5zDH</t>
+  </si>
+  <si>
+    <t>marketing tools</t>
+  </si>
+  <si>
+    <t>reward campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit timing should be according to all rewards </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 should be replaced with number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">many things are static they should be according to all rewards </t>
+  </si>
+  <si>
+    <t>make a separate page for admin earnings with detailed breakdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if funding source is seller than seller / shop name dropdown should be there </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if funding source is brand than brand name dropdown should appear </t>
+  </si>
+  <si>
+    <t>if funding source is shared then there should be an option to choose seller and than percentage should be asked how much % seller will bear and how much % admin will bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">define priority and its logic if not needed remove it if needed than write explainable name </t>
+  </si>
+  <si>
+    <t>flat discount coupon --&gt; remove max discount cap as it will is same as flat amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all types of rewards --&gt; start date should not be set in past </t>
+  </si>
+  <si>
+    <t xml:space="preserve">all types of rewards --&gt; end date should not be set in past and should not be before start date </t>
+  </si>
+  <si>
+    <t xml:space="preserve">remove budget limits from free delivery rewards </t>
+  </si>
+  <si>
+    <t>click back</t>
+  </si>
+  <si>
+    <t>it should not show exit app notification instead should redirect to previous page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rewards </t>
+  </si>
+  <si>
+    <t>reward campaign coupons are not visible on checkout</t>
+  </si>
+  <si>
+    <t>remove terms and privacy from otp page</t>
+  </si>
+  <si>
+    <t>all levels</t>
+  </si>
+  <si>
+    <t>if admin didn't upload any photo --&gt; it should show default photo instead of category name</t>
+  </si>
+  <si>
+    <t>login/signup</t>
+  </si>
+  <si>
+    <t>terms &amp; conditions</t>
+  </si>
+  <si>
+    <t>item added in cart should not be visible in terms &amp; conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getting too many otp expired toast messages together </t>
+  </si>
+  <si>
+    <t>timeout functionality is not working correctly - on resend the it timeouts automatically</t>
+  </si>
+  <si>
+    <t>cart</t>
+  </si>
+  <si>
+    <t>available coupon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if coupon or reward is not assigned to user than those coupon and rewards should be visible to that user </t>
+  </si>
+  <si>
+    <t>login /signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">support centre should be there before user logins (can be on login / signup) as they may need support during login or sign up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">edit sellers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">message owner is not working </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/WA370c8OR9i2</t>
+  </si>
+  <si>
+    <t>send alert is not working</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/EDWEDUeC0wrg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when seller is under review - it should show a small pop up in which only name number email should be present - or make a separate page for shop and seller review </t>
+  </si>
+  <si>
+    <t xml:space="preserve">category </t>
+  </si>
+  <si>
+    <t xml:space="preserve">add new category --&gt; category name --&gt; add space between name or add big capital letter --&gt; than it can make category </t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin should get the notification and a red dot count or this page if new shop registered </t>
+  </si>
+  <si>
+    <t>view --&gt;if more than one header category is chosen  by seller --&gt; still shows one category name partner only</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/kkVkdARW9XPw</t>
+  </si>
+  <si>
+    <t>all pages (categories , catalog etc ) should have default images if admin , seller or delivery does not upload any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manage all store </t>
+  </si>
+  <si>
+    <t xml:space="preserve">import catalogue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bundle --&gt; it should show all the products under it too </t>
+  </si>
+  <si>
+    <t xml:space="preserve">one product is taking too much of space vertically  --&gt; align information beside one another so one row can have 2 details </t>
+  </si>
+  <si>
+    <t xml:space="preserve">select rejected store </t>
+  </si>
+  <si>
+    <t>rejected store should not open its dashboard</t>
+  </si>
+  <si>
+    <t>product details</t>
+  </si>
+  <si>
+    <t>shelf life , country of origin , fssai license  are static - not asked from seller they should be dynamic</t>
+  </si>
+  <si>
+    <t>the product added by seller is not visible in categories or home page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commissions are not working correctly </t>
+  </si>
+  <si>
+    <t>flow paused - 12/09</t>
+  </si>
+  <si>
+    <t>gst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both gst should be in one row only - also add dropdown for charges </t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount is mismatching - total is floating point and total amount is in decimal number </t>
+  </si>
+  <si>
+    <t>slide to place order --&gt; remove | and rupee sign</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/T72HEjSLrSLd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add item to this order </t>
+  </si>
+  <si>
+    <t>item images are not updating on this page - and if there no image a default image should be there</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/qHqOjGDWSqt6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add item to order --&gt; the button is overlapping </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/3w6OiCXc9xAs</t>
+  </si>
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">view </t>
+  </si>
+  <si>
+    <t>if customers add products after order - it should ask seller acceptance</t>
+  </si>
+  <si>
+    <t>the items are not showing with commission</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/y86-cEXe_bDP</t>
+  </si>
+  <si>
+    <t>change the ui when seller is awaiting customer approval</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/EaF0esZofDi3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if seller reduce the order --&gt; it should show proper information about product and quantity </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/eVi8GH3COhug</t>
+  </si>
+  <si>
+    <t>not fetching location - even through device location is on</t>
+  </si>
+  <si>
+    <t>flow pauused - 17- 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set price &amp; publish </t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock --&gt; 0 should be removed while writing stock </t>
+  </si>
+  <si>
+    <t xml:space="preserve">active sellers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">edit details --&gt; save details --&gt; show seller not found </t>
+  </si>
+  <si>
+    <t>edit details --&gt;description and location should be present in edit details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">on some products --&gt; commission is not applying </t>
+  </si>
+  <si>
+    <t xml:space="preserve">new order pop up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin commission for product that is given by user should not be visible to seller --&gt; if commission is applicable on seller level by admin than only commission should be visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sort by filter </t>
+  </si>
+  <si>
+    <t>sort by filter are not working correctly - and also they should not be sorted out according to store</t>
+  </si>
+  <si>
+    <t>share on header --&gt; on click it gives toast message of item shared successfully even when item is shared on any app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filters --&gt; the page is scrolling horizontally because of filters </t>
+  </si>
+  <si>
+    <t>filters --&gt; add necessary filters like price range , brand etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product details --&gt; should show all necessary information provided by seller / admin like brand </t>
+  </si>
+  <si>
+    <t>status should be visible only at one place --&gt; there are 2 status showing same thing remove one</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/i0gZT_wTGSsl</t>
+  </si>
+  <si>
+    <t>add product to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if availability is turned off by seller --&gt; and user try to add product to cart it misbehaves and shows --&gt; product added to cart and product unavailable toast message together </t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if product is hidden --&gt; availability should turn off automatically and if availability is turned on product should be removed from hidden </t>
+  </si>
+  <si>
+    <t>if product availability is turned off  --&gt; product should automatically be hidden --&gt; the two of them should work coordinately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">push  notification </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if seller adjusts the price by 100 less --&gt; the push notification still show seller demanding extra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the correct product amount (+ commission amount )should be visible on track order page and invoice and other places </t>
+  </si>
+  <si>
+    <t>if product in cart is hidden or unavailable --&gt; it should show proper validation message in cart that product is unavailable --&gt; currently it removes product from cart until its hidden and if it's unavailable it doesn't fetch location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">view - replacement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the replacement tab should open above view tab --&gt; currently it is opening under view </t>
+  </si>
+  <si>
+    <t xml:space="preserve">replacement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">instead of #1 or # 2 it should show item name </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/gOmZFgMAgSdL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">didn't get push notification for replacement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">wallet  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the button at the end is not fully visible </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/fWHKmJctqAMv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">there should be a way to see a refund history </t>
+  </si>
+  <si>
+    <t>login page is not scrolling on web</t>
+  </si>
+  <si>
+    <t>support icon is not visible correctly</t>
+  </si>
+  <si>
+    <t>support --&gt;chat , raise ticket should work before login --&gt; as user may need help/support regarding login /signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if two orders are placing together it shows wrong validation on other user --&gt; multiple users should be able to login and order at the same time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if item quantity is 1 and the product is present in multiple cart --&gt; it should show validation of out of stock product --&gt; order should be placed only if there is a stock of item </t>
+  </si>
+  <si>
+    <t xml:space="preserve">use wallet amount --&gt; place order --&gt; not able to place order and it shows backend details in toast message </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/3sT8N_v2TvNg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new order pop up / orders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">order id should be smaller in seller </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if seller does not accept order in time --&gt; it shows order not found on both user and seller app </t>
+  </si>
+  <si>
+    <t xml:space="preserve">on seller app --&gt; order should go in pending state and in some hour if they don't change status to confirm it should give push notification that order will be cancelled in some time and then cancel and user should get the order cancelled notification - not that order not found </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if usage limit of an coupon is reached --&gt; it should not be visible to users </t>
+  </si>
+  <si>
+    <t xml:space="preserve">marketing tools </t>
+  </si>
+  <si>
+    <t>coupon &amp; promos</t>
+  </si>
+  <si>
+    <t>if usage limit is reached the coupon should be deactivated automatically on admin</t>
+  </si>
+  <si>
+    <t>if usage limit left is 1 and 2 people applied the same coupon than on placing order it should not be showing backend toast message of conflict</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/evyUuuSF9tCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">place online order --&gt; it shows something went wrong </t>
+  </si>
+  <si>
+    <t>change status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if order is not available for acceptable or expired --&gt; it should change the status of the order to cancelled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile photo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile photo and background page is not visible </t>
+  </si>
+  <si>
+    <t>https://prnt.sc/Yv3RD8Ld-PwO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price revision kk bad delivery ko notification nhi aya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">reward &amp; wallet </t>
+  </si>
+  <si>
+    <t>my referral --&gt; referral should not be successful until new user registers and complete order</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/UIcbo26f8aFZ</t>
+  </si>
+  <si>
+    <t>my referral --&gt; history --&gt; remove code , friend --&gt; instead of friend user that registers name should be there</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you might also like </t>
+  </si>
+  <si>
+    <t>out of stock addons should not be visible on cart</t>
+  </si>
+  <si>
+    <t>only product from same store should visible in this section</t>
+  </si>
+  <si>
+    <t>schedule now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schedule 6-9 --&gt; close schedule --&gt; reopen schedule --&gt; the time chosen shows default chosen instead of what user chosen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">place order should not appear here </t>
+  </si>
+  <si>
+    <t>notification</t>
+  </si>
+  <si>
+    <t>getting 2 push notification for each action</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/30SZRtVkMeqf</t>
+  </si>
+  <si>
+    <t>different location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recommended for you --&gt; stores for different location should not be viisible here </t>
+  </si>
+  <si>
+    <t xml:space="preserve">super ad placement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ads of diiferent location / zone should not be visible here </t>
+  </si>
+  <si>
+    <t xml:space="preserve">shows service unavailable in areas  --&gt; it should show category product is not available </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccategory that has product in that location should be appeared on top </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sellers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">there should be a dropdown/hierarchy in each seller where all its store and their information is visible </t>
+  </si>
+  <si>
+    <t>if commission is edited on categories --&gt;it should be making changes on userr app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add new campaign --&gt; cashback &amp; rewards --&gt; new shop promotion &amp; shop wise commission --&gt; sellers /stores are not visible in dropdown </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1077,6 +1734,10 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1099,7 +1760,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1127,8 +1788,20 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1439,6 +2112,8 @@
     <col customWidth="1" min="5" max="5" width="52.25"/>
     <col customWidth="1" min="6" max="6" width="20.5"/>
     <col customWidth="1" min="7" max="8" width="21.0"/>
+    <col customWidth="1" min="9" max="9" width="47.13"/>
+    <col customWidth="1" min="13" max="13" width="28.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1681,8 +2356,8 @@
         <v>28</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="9" t="s">
-        <v>24</v>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>29</v>
@@ -1855,8 +2530,8 @@
         <v>40</v>
       </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="9" t="s">
-        <v>24</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>15</v>
@@ -1898,8 +2573,8 @@
         <v>41</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="9" t="s">
-        <v>24</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>32</v>
@@ -1943,8 +2618,8 @@
         <v>44</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="9" t="s">
-        <v>24</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>29</v>
@@ -1988,8 +2663,8 @@
         <v>47</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="9" t="s">
-        <v>24</v>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>15</v>
@@ -2031,8 +2706,8 @@
         <v>50</v>
       </c>
       <c r="F14" s="7"/>
-      <c r="G14" s="9" t="s">
-        <v>24</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>35</v>
@@ -2074,8 +2749,8 @@
         <v>51</v>
       </c>
       <c r="F15" s="7"/>
-      <c r="G15" s="9" t="s">
-        <v>24</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>15</v>
@@ -2117,8 +2792,8 @@
         <v>52</v>
       </c>
       <c r="F16" s="7"/>
-      <c r="G16" s="9" t="s">
-        <v>24</v>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>15</v>
@@ -2159,14 +2834,18 @@
       <c r="E17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="9" t="s">
-        <v>24</v>
+      <c r="F17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="7"/>
+      <c r="I17" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2197,14 +2876,14 @@
         <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18" s="7"/>
-      <c r="G18" s="9" t="s">
-        <v>24</v>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>29</v>
@@ -2243,11 +2922,11 @@
         <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F19" s="7"/>
-      <c r="G19" s="9" t="s">
-        <v>24</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>35</v>
@@ -2280,17 +2959,17 @@
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="7"/>
-      <c r="G20" s="9" t="s">
-        <v>24</v>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>35</v>
@@ -2323,17 +3002,17 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F21" s="7"/>
-      <c r="G21" s="9" t="s">
-        <v>24</v>
+      <c r="G21" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>35</v>
@@ -2365,23 +3044,23 @@
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F22" s="7"/>
-      <c r="G22" s="9" t="s">
-        <v>24</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -2410,21 +3089,21 @@
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F23" s="7"/>
-      <c r="G23" s="9" t="s">
-        <v>24</v>
+      <c r="G23" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>29</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -2453,13 +3132,13 @@
         <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="9" t="s">
@@ -2496,22 +3175,24 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F25" s="7"/>
-      <c r="G25" s="9" t="s">
-        <v>24</v>
+      <c r="G25" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="7"/>
+      <c r="I25" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2539,15 +3220,15 @@
         <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F26" s="7"/>
-      <c r="G26" s="9" t="s">
-        <v>24</v>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>29</v>
@@ -2577,25 +3258,25 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="9" t="s">
-        <v>24</v>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2620,20 +3301,20 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F28" s="7"/>
-      <c r="G28" s="9" t="s">
-        <v>24</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>35</v>
@@ -2663,21 +3344,23 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F29" s="7"/>
-      <c r="G29" s="9" t="s">
-        <v>24</v>
+      <c r="G29" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="7"/>
+      <c r="I29" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2708,14 +3391,14 @@
         <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F30" s="7"/>
-      <c r="G30" s="9" t="s">
-        <v>24</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -2748,17 +3431,17 @@
         <v>20</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="9" t="s">
-        <v>24</v>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>35</v>
@@ -2791,17 +3474,17 @@
         <v>20</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F32" s="7"/>
-      <c r="G32" s="9" t="s">
-        <v>24</v>
+      <c r="G32" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>29</v>
@@ -2834,24 +3517,26 @@
         <v>20</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>24</v>
+        <v>94</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="7"/>
+      <c r="I33" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2879,17 +3564,17 @@
         <v>20</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F34" s="7"/>
-      <c r="G34" s="9" t="s">
-        <v>24</v>
+      <c r="G34" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>32</v>
@@ -2922,19 +3607,19 @@
         <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>24</v>
+        <v>102</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
@@ -2967,17 +3652,17 @@
         <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F36" s="7"/>
-      <c r="G36" s="9" t="s">
-        <v>24</v>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>15</v>
@@ -3010,17 +3695,17 @@
         <v>9</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F37" s="7"/>
-      <c r="G37" s="9" t="s">
-        <v>24</v>
+      <c r="G37" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>32</v>
@@ -3050,20 +3735,20 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F38" s="7"/>
-      <c r="G38" s="9" t="s">
-        <v>24</v>
+      <c r="G38" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>32</v>
@@ -3093,20 +3778,22 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="9" t="s">
-        <v>24</v>
+        <v>108</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>32</v>
@@ -3136,20 +3823,20 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F40" s="7"/>
-      <c r="G40" s="9" t="s">
-        <v>24</v>
+      <c r="G40" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>32</v>
@@ -3179,20 +3866,20 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F41" s="7"/>
-      <c r="G41" s="9" t="s">
-        <v>24</v>
+      <c r="G41" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>35</v>
@@ -3222,20 +3909,20 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F42" s="7"/>
-      <c r="G42" s="9" t="s">
-        <v>24</v>
+      <c r="G42" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>29</v>
@@ -3268,19 +3955,19 @@
         <v>9</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>24</v>
+        <v>118</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>15</v>
@@ -3313,17 +4000,17 @@
         <v>9</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F44" s="7"/>
-      <c r="G44" s="9" t="s">
-        <v>24</v>
+      <c r="G44" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>15</v>
@@ -3353,18 +4040,18 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F45" s="7"/>
-      <c r="G45" s="9" t="s">
-        <v>24</v>
+      <c r="G45" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>35</v>
@@ -3397,17 +4084,17 @@
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F46" s="7"/>
-      <c r="G46" s="9" t="s">
-        <v>24</v>
+      <c r="G46" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>35</v>
@@ -3440,17 +4127,17 @@
         <v>20</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F47" s="7"/>
-      <c r="G47" s="9" t="s">
-        <v>24</v>
+      <c r="G47" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>35</v>
@@ -3483,17 +4170,17 @@
         <v>20</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F48" s="7"/>
-      <c r="G48" s="9" t="s">
-        <v>24</v>
+      <c r="G48" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>32</v>
@@ -3526,17 +4213,17 @@
         <v>20</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F49" s="7"/>
-      <c r="G49" s="9" t="s">
-        <v>24</v>
+      <c r="G49" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>32</v>
@@ -3569,17 +4256,17 @@
         <v>20</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F50" s="7"/>
-      <c r="G50" s="9" t="s">
-        <v>24</v>
+      <c r="G50" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>15</v>
@@ -3612,17 +4299,17 @@
         <v>20</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F51" s="7"/>
-      <c r="G51" s="9" t="s">
-        <v>24</v>
+      <c r="G51" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>15</v>
@@ -3655,19 +4342,19 @@
         <v>20</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>24</v>
+        <v>131</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>15</v>
@@ -3700,22 +4387,24 @@
         <v>20</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F53" s="7"/>
-      <c r="G53" s="9" t="s">
-        <v>24</v>
+      <c r="G53" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I53" s="7"/>
+      <c r="I53" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3743,17 +4432,17 @@
         <v>20</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F54" s="7"/>
-      <c r="G54" s="9" t="s">
-        <v>24</v>
+      <c r="G54" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>29</v>
@@ -3786,17 +4475,17 @@
         <v>20</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F55" s="7"/>
-      <c r="G55" s="9" t="s">
-        <v>24</v>
+      <c r="G55" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>35</v>
@@ -3826,22 +4515,22 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>24</v>
+        <v>141</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>35</v>
@@ -3851,7 +4540,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -3873,20 +4562,20 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F57" s="7"/>
-      <c r="G57" s="9" t="s">
-        <v>24</v>
+      <c r="G57" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>15</v>
@@ -3919,17 +4608,17 @@
         <v>20</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F58" s="7"/>
-      <c r="G58" s="9" t="s">
-        <v>24</v>
+      <c r="G58" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>15</v>
@@ -3962,17 +4651,17 @@
         <v>20</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F59" s="7"/>
-      <c r="G59" s="9" t="s">
-        <v>24</v>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>32</v>
@@ -4002,18 +4691,18 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F60" s="7"/>
-      <c r="G60" s="9" t="s">
-        <v>24</v>
+      <c r="G60" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>29</v>
@@ -4043,25 +4732,27 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F61" s="7"/>
-      <c r="G61" s="9" t="s">
-        <v>24</v>
+      <c r="G61" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -4089,17 +4780,17 @@
         <v>9</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F62" s="7"/>
-      <c r="G62" s="9" t="s">
-        <v>24</v>
+      <c r="G62" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>35</v>
@@ -4132,17 +4823,17 @@
         <v>9</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F63" s="7"/>
-      <c r="G63" s="9" t="s">
-        <v>24</v>
+      <c r="G63" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>32</v>
@@ -4172,22 +4863,22 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>24</v>
+        <v>162</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>32</v>
@@ -4217,27 +4908,29 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D65" s="3" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>24</v>
+        <v>165</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I65" s="7"/>
+      <c r="I65" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -4262,20 +4955,20 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F66" s="7"/>
-      <c r="G66" s="9" t="s">
-        <v>24</v>
+      <c r="G66" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>32</v>
@@ -4305,20 +4998,20 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F67" s="7"/>
-      <c r="G67" s="9" t="s">
-        <v>24</v>
+      <c r="G67" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>15</v>
@@ -4348,20 +5041,22 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="9" t="s">
-        <v>24</v>
+        <v>173</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>15</v>
@@ -4391,20 +5086,20 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F69" s="7"/>
-      <c r="G69" s="9" t="s">
-        <v>24</v>
+      <c r="G69" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>15</v>
@@ -4434,20 +5129,20 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F70" s="7"/>
-      <c r="G70" s="9" t="s">
-        <v>24</v>
+      <c r="G70" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>29</v>
@@ -4477,18 +5172,18 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="F71" s="7"/>
-      <c r="G71" s="9" t="s">
-        <v>24</v>
+      <c r="G71" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>29</v>
@@ -4518,20 +5213,20 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F72" s="7"/>
-      <c r="G72" s="9" t="s">
-        <v>24</v>
+      <c r="G72" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>35</v>
@@ -4561,20 +5256,20 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F73" s="7"/>
-      <c r="G73" s="9" t="s">
-        <v>24</v>
+      <c r="G73" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>15</v>
@@ -4607,22 +5302,22 @@
         <v>9</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F74" s="7"/>
-      <c r="G74" s="9" t="s">
-        <v>24</v>
+      <c r="G74" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I74" s="7"/>
+      <c r="I74" s="3"/>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4650,17 +5345,17 @@
         <v>9</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="F75" s="7"/>
-      <c r="G75" s="9" t="s">
-        <v>24</v>
+      <c r="G75" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>15</v>
@@ -4693,16 +5388,16 @@
         <v>9</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>24</v>
+        <v>186</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>35</v>
@@ -4735,19 +5430,19 @@
         <v>9</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>24</v>
+        <v>189</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>35</v>
@@ -4780,17 +5475,17 @@
         <v>9</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F78" s="7"/>
-      <c r="G78" s="9" t="s">
-        <v>24</v>
+      <c r="G78" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>35</v>
@@ -4823,17 +5518,17 @@
         <v>9</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F79" s="7"/>
-      <c r="G79" s="9" t="s">
-        <v>24</v>
+      <c r="G79" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>35</v>
@@ -4866,17 +5561,17 @@
         <v>9</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F80" s="7"/>
-      <c r="G80" s="9" t="s">
-        <v>24</v>
+      <c r="G80" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>32</v>
@@ -4909,17 +5604,17 @@
         <v>9</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F81" s="7"/>
-      <c r="G81" s="9" t="s">
-        <v>24</v>
+      <c r="G81" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>32</v>
@@ -4952,17 +5647,17 @@
         <v>20</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F82" s="7"/>
-      <c r="G82" s="9" t="s">
-        <v>24</v>
+      <c r="G82" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>29</v>
@@ -4995,17 +5690,17 @@
         <v>20</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F83" s="7"/>
-      <c r="G83" s="9" t="s">
-        <v>24</v>
+      <c r="G83" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>32</v>
@@ -5035,20 +5730,20 @@
         <v>83.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F84" s="7"/>
-      <c r="G84" s="9" t="s">
-        <v>24</v>
+      <c r="G84" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>32</v>
@@ -5078,22 +5773,22 @@
         <v>84.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>24</v>
+        <v>201</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>15</v>
@@ -5123,20 +5818,20 @@
         <v>85.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F86" s="7"/>
-      <c r="G86" s="9" t="s">
-        <v>24</v>
+      <c r="G86" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>15</v>
@@ -5166,20 +5861,20 @@
         <v>86.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F87" s="7"/>
-      <c r="G87" s="9" t="s">
-        <v>24</v>
+      <c r="G87" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>32</v>
@@ -5209,20 +5904,20 @@
         <v>87.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F88" s="7"/>
-      <c r="G88" s="9" t="s">
-        <v>24</v>
+      <c r="G88" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>35</v>
@@ -5255,17 +5950,17 @@
         <v>9</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F89" s="7"/>
-      <c r="G89" s="9" t="s">
-        <v>24</v>
+      <c r="G89" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>32</v>
@@ -5298,17 +5993,17 @@
         <v>9</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F90" s="7"/>
-      <c r="G90" s="9" t="s">
-        <v>24</v>
+      <c r="G90" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>29</v>
@@ -5341,17 +6036,17 @@
         <v>9</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F91" s="7"/>
-      <c r="G91" s="9" t="s">
-        <v>24</v>
+      <c r="G91" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>29</v>
@@ -5384,17 +6079,17 @@
         <v>9</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="F92" s="7"/>
-      <c r="G92" s="9" t="s">
-        <v>24</v>
+      <c r="G92" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>32</v>
@@ -5427,17 +6122,17 @@
         <v>9</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="F93" s="7"/>
-      <c r="G93" s="9" t="s">
-        <v>24</v>
+      <c r="G93" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>32</v>
@@ -5470,17 +6165,17 @@
         <v>9</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>24</v>
+        <v>216</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>32</v>
@@ -5513,19 +6208,19 @@
         <v>9</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>24</v>
+        <v>220</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>15</v>
@@ -5555,22 +6250,22 @@
         <v>95.0</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>24</v>
+        <v>224</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>15</v>
@@ -5600,18 +6295,18 @@
         <v>96.0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="3" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F97" s="7"/>
-      <c r="G97" s="9" t="s">
-        <v>24</v>
+      <c r="G97" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>15</v>
@@ -5641,18 +6336,18 @@
         <v>97.0</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F98" s="7"/>
-      <c r="G98" s="9" t="s">
-        <v>24</v>
+      <c r="G98" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>15</v>
@@ -5687,10 +6382,10 @@
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="F99" s="7"/>
-      <c r="G99" s="9" t="s">
+      <c r="G99" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H99" s="6" t="s">
@@ -5728,11 +6423,11 @@
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F100" s="7"/>
-      <c r="G100" s="9" t="s">
-        <v>24</v>
+      <c r="G100" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>35</v>
@@ -5762,7 +6457,7 @@
         <v>100.0</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>10</v>
@@ -5771,11 +6466,11 @@
         <v>25</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="F101" s="7"/>
-      <c r="G101" s="9" t="s">
-        <v>24</v>
+      <c r="G101" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>29</v>
@@ -5805,20 +6500,20 @@
         <v>101.0</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="F102" s="7"/>
-      <c r="G102" s="9" t="s">
-        <v>24</v>
+      <c r="G102" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>29</v>
@@ -5848,18 +6543,18 @@
         <v>102.0</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="8" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="F103" s="7"/>
-      <c r="G103" s="9" t="s">
-        <v>24</v>
+      <c r="G103" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>35</v>
@@ -5889,20 +6584,20 @@
         <v>103.0</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="F104" s="7"/>
-      <c r="G104" s="9" t="s">
-        <v>24</v>
+      <c r="G104" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>32</v>
@@ -5932,20 +6627,20 @@
         <v>104.0</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F105" s="7"/>
-      <c r="G105" s="9" t="s">
-        <v>24</v>
+      <c r="G105" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>35</v>
@@ -5978,17 +6673,17 @@
         <v>9</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="F106" s="7"/>
-      <c r="G106" s="9" t="s">
-        <v>24</v>
+      <c r="G106" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>35</v>
@@ -6021,17 +6716,17 @@
         <v>9</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F107" s="7"/>
-      <c r="G107" s="9" t="s">
-        <v>24</v>
+      <c r="G107" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>32</v>
@@ -6064,17 +6759,17 @@
         <v>9</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="F108" s="7"/>
-      <c r="G108" s="9" t="s">
-        <v>24</v>
+      <c r="G108" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>15</v>
@@ -6107,17 +6802,17 @@
         <v>9</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F109" s="7"/>
-      <c r="G109" s="9" t="s">
-        <v>24</v>
+      <c r="G109" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>32</v>
@@ -6148,17 +6843,17 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="3" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>24</v>
+        <v>248</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>35</v>
@@ -6188,18 +6883,18 @@
         <v>110.0</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D111" s="7"/>
       <c r="E111" s="3" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="F111" s="7"/>
-      <c r="G111" s="9" t="s">
-        <v>24</v>
+      <c r="G111" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>15</v>
@@ -6229,20 +6924,20 @@
         <v>111.0</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F112" s="7"/>
-      <c r="G112" s="9" t="s">
-        <v>24</v>
+      <c r="G112" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>32</v>
@@ -6272,20 +6967,20 @@
         <v>112.0</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F113" s="7"/>
-      <c r="G113" s="9" t="s">
-        <v>24</v>
+      <c r="G113" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>29</v>
@@ -6318,17 +7013,17 @@
         <v>9</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="F114" s="7"/>
-      <c r="G114" s="9" t="s">
-        <v>24</v>
+      <c r="G114" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>32</v>
@@ -6361,17 +7056,17 @@
         <v>20</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F115" s="7"/>
-      <c r="G115" s="9" t="s">
-        <v>24</v>
+      <c r="G115" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>29</v>
@@ -6404,15 +7099,15 @@
         <v>20</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F116" s="7"/>
-      <c r="G116" s="9" t="s">
-        <v>24</v>
+      <c r="G116" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>15</v>
@@ -6445,17 +7140,17 @@
         <v>20</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="F117" s="7"/>
-      <c r="G117" s="9" t="s">
-        <v>24</v>
+      <c r="G117" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>29</v>
@@ -6485,21 +7180,21 @@
         <v>117.0</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="3" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="F118" s="7"/>
-      <c r="G118" s="9" t="s">
-        <v>24</v>
+      <c r="G118" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
@@ -6526,18 +7221,18 @@
         <v>118.0</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="3" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F119" s="7"/>
-      <c r="G119" s="9" t="s">
-        <v>24</v>
+      <c r="G119" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>32</v>
@@ -6567,16 +7262,16 @@
         <v>119.0</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F120" s="7"/>
-      <c r="G120" s="9" t="s">
-        <v>24</v>
+      <c r="G120" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>29</v>
@@ -6606,18 +7301,18 @@
         <v>120.0</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F121" s="7"/>
-      <c r="G121" s="9" t="s">
-        <v>24</v>
+      <c r="G121" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>35</v>
@@ -6647,20 +7342,20 @@
         <v>121.0</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F122" s="7"/>
-      <c r="G122" s="9" t="s">
-        <v>24</v>
+      <c r="G122" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>32</v>
@@ -6690,18 +7385,18 @@
         <v>122.0</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="F123" s="7"/>
-      <c r="G123" s="9" t="s">
-        <v>24</v>
+      <c r="G123" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>32</v>
@@ -6731,20 +7426,20 @@
         <v>123.0</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="F124" s="7"/>
-      <c r="G124" s="9" t="s">
-        <v>24</v>
+      <c r="G124" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>32</v>
@@ -6774,20 +7469,20 @@
         <v>124.0</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="F125" s="7"/>
-      <c r="G125" s="9" t="s">
-        <v>24</v>
+      <c r="G125" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>32</v>
@@ -6820,15 +7515,15 @@
         <v>20</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F126" s="7"/>
-      <c r="G126" s="9" t="s">
-        <v>24</v>
+      <c r="G126" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>32</v>
@@ -6861,15 +7556,15 @@
         <v>20</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="3" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="F127" s="7"/>
-      <c r="G127" s="9" t="s">
-        <v>24</v>
+      <c r="G127" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>32</v>
@@ -6902,17 +7597,17 @@
         <v>20</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F128" s="7"/>
-      <c r="G128" s="9" t="s">
-        <v>24</v>
+      <c r="G128" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>35</v>
@@ -6945,17 +7640,17 @@
         <v>20</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="F129" s="7"/>
-      <c r="G129" s="9" t="s">
-        <v>24</v>
+      <c r="G129" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>32</v>
@@ -6988,13 +7683,13 @@
         <v>20</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="F130" s="7"/>
       <c r="G130" s="9" t="s">
@@ -7031,17 +7726,17 @@
         <v>20</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="F131" s="7"/>
-      <c r="G131" s="9" t="s">
-        <v>24</v>
+      <c r="G131" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>15</v>
@@ -7074,17 +7769,17 @@
         <v>20</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="F132" s="7"/>
-      <c r="G132" s="9" t="s">
-        <v>24</v>
+      <c r="G132" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>15</v>
@@ -7117,17 +7812,17 @@
         <v>20</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="F133" s="7"/>
-      <c r="G133" s="9" t="s">
-        <v>24</v>
+      <c r="G133" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>15</v>
@@ -7157,18 +7852,18 @@
         <v>133.0</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="3" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F134" s="7"/>
-      <c r="G134" s="9" t="s">
-        <v>24</v>
+      <c r="G134" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>29</v>
@@ -7198,18 +7893,18 @@
         <v>134.0</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="3" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="F135" s="7"/>
-      <c r="G135" s="9" t="s">
-        <v>24</v>
+      <c r="G135" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>29</v>
@@ -7239,22 +7934,22 @@
         <v>135.0</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G136" s="9" t="s">
-        <v>24</v>
+        <v>293</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>15</v>
@@ -7287,17 +7982,17 @@
         <v>20</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="F137" s="7"/>
-      <c r="G137" s="9" t="s">
-        <v>24</v>
+      <c r="G137" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>35</v>
@@ -7330,17 +8025,17 @@
         <v>20</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="F138" s="7"/>
-      <c r="G138" s="9" t="s">
-        <v>24</v>
+      <c r="G138" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>32</v>
@@ -7373,17 +8068,17 @@
         <v>20</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="F139" s="7"/>
-      <c r="G139" s="9" t="s">
-        <v>24</v>
+      <c r="G139" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>35</v>
@@ -7416,15 +8111,15 @@
         <v>20</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="3" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="F140" s="7"/>
-      <c r="G140" s="9" t="s">
-        <v>24</v>
+      <c r="G140" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>35</v>
@@ -7457,17 +8152,17 @@
         <v>20</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="F141" s="7"/>
-      <c r="G141" s="9" t="s">
-        <v>24</v>
+      <c r="G141" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H141" s="6" t="s">
         <v>15</v>
@@ -7500,19 +8195,19 @@
         <v>20</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="G142" s="9" t="s">
-        <v>24</v>
+        <v>304</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>15</v>
@@ -7545,13 +8240,13 @@
         <v>20</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F143" s="7"/>
       <c r="G143" s="9" t="s">
@@ -7588,13 +8283,13 @@
         <v>20</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="F144" s="7"/>
       <c r="G144" s="9" t="s">
@@ -7628,18 +8323,18 @@
         <v>144.0</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D145" s="7"/>
       <c r="E145" s="3" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="F145" s="7"/>
-      <c r="G145" s="9" t="s">
-        <v>24</v>
+      <c r="G145" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>29</v>
@@ -7669,20 +8364,20 @@
         <v>145.0</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="F146" s="7"/>
-      <c r="G146" s="9" t="s">
-        <v>24</v>
+      <c r="G146" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>15</v>
@@ -7712,20 +8407,20 @@
         <v>146.0</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="F147" s="7"/>
-      <c r="G147" s="9" t="s">
-        <v>24</v>
+      <c r="G147" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>35</v>
@@ -7755,20 +8450,20 @@
         <v>147.0</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="F148" s="7"/>
-      <c r="G148" s="9" t="s">
-        <v>24</v>
+      <c r="G148" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>32</v>
@@ -7798,20 +8493,20 @@
         <v>148.0</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="F149" s="7"/>
-      <c r="G149" s="9" t="s">
-        <v>24</v>
+      <c r="G149" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H149" s="6" t="s">
         <v>32</v>
@@ -7841,20 +8536,20 @@
         <v>149.0</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="F150" s="7"/>
-      <c r="G150" s="9" t="s">
-        <v>24</v>
+      <c r="G150" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>15</v>
@@ -7887,15 +8582,15 @@
         <v>20</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="3" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="F151" s="7"/>
-      <c r="G151" s="9" t="s">
-        <v>24</v>
+      <c r="G151" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H151" s="6" t="s">
         <v>15</v>
@@ -7925,20 +8620,20 @@
         <v>151.0</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F152" s="7"/>
-      <c r="G152" s="9" t="s">
-        <v>24</v>
+      <c r="G152" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>15</v>
@@ -7971,15 +8666,15 @@
         <v>20</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D153" s="7"/>
       <c r="E153" s="3" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="F153" s="7"/>
-      <c r="G153" s="9" t="s">
-        <v>24</v>
+      <c r="G153" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>29</v>
@@ -8012,15 +8707,15 @@
         <v>20</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="3" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="F154" s="7"/>
-      <c r="G154" s="9" t="s">
-        <v>24</v>
+      <c r="G154" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>35</v>
@@ -8053,15 +8748,15 @@
         <v>20</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="3" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="F155" s="7"/>
-      <c r="G155" s="9" t="s">
-        <v>24</v>
+      <c r="G155" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H155" s="6" t="s">
         <v>15</v>
@@ -8094,17 +8789,17 @@
         <v>20</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="F156" s="7"/>
-      <c r="G156" s="9" t="s">
-        <v>24</v>
+      <c r="G156" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>32</v>
@@ -8137,17 +8832,17 @@
         <v>20</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="F157" s="7"/>
-      <c r="G157" s="9" t="s">
-        <v>24</v>
+      <c r="G157" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>35</v>
@@ -8180,15 +8875,15 @@
         <v>20</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D158" s="7"/>
       <c r="E158" s="3" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="F158" s="7"/>
-      <c r="G158" s="9" t="s">
-        <v>24</v>
+      <c r="G158" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>32</v>
@@ -8218,18 +8913,18 @@
         <v>158.0</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="3" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="F159" s="7"/>
-      <c r="G159" s="9" t="s">
-        <v>24</v>
+      <c r="G159" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>32</v>
@@ -8262,17 +8957,17 @@
         <v>20</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="F160" s="7"/>
-      <c r="G160" s="9" t="s">
-        <v>24</v>
+      <c r="G160" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>32</v>
@@ -8305,15 +9000,15 @@
         <v>20</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D161" s="7"/>
       <c r="E161" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="F161" s="7"/>
-      <c r="G161" s="9" t="s">
-        <v>24</v>
+      <c r="G161" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>15</v>
@@ -8343,18 +9038,18 @@
         <v>161.0</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="D162" s="7"/>
       <c r="E162" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F162" s="7"/>
-      <c r="G162" s="9" t="s">
-        <v>24</v>
+      <c r="G162" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>15</v>
@@ -8384,18 +9079,18 @@
         <v>162.0</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D163" s="7"/>
       <c r="E163" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="F163" s="7"/>
-      <c r="G163" s="9" t="s">
-        <v>24</v>
+      <c r="G163" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>29</v>
@@ -8425,20 +9120,20 @@
         <v>163.0</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="F164" s="7"/>
-      <c r="G164" s="9" t="s">
-        <v>24</v>
+      <c r="G164" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>35</v>
@@ -8468,20 +9163,20 @@
         <v>164.0</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="F165" s="7"/>
-      <c r="G165" s="9" t="s">
-        <v>24</v>
+      <c r="G165" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>29</v>
@@ -8514,19 +9209,19 @@
         <v>20</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="G166" s="9" t="s">
-        <v>24</v>
+        <v>346</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>15</v>
@@ -8556,18 +9251,18 @@
         <v>166.0</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="F167" s="7"/>
-      <c r="G167" s="9" t="s">
-        <v>24</v>
+      <c r="G167" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>32</v>
@@ -8600,17 +9295,17 @@
         <v>20</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F168" s="7"/>
-      <c r="G168" s="9" t="s">
-        <v>24</v>
+      <c r="G168" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>15</v>
@@ -8643,17 +9338,17 @@
         <v>20</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="F169" s="7"/>
-      <c r="G169" s="9" t="s">
-        <v>24</v>
+      <c r="G169" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>35</v>
@@ -8683,22 +9378,22 @@
         <v>169.0</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G170" s="9" t="s">
-        <v>24</v>
+        <v>355</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>15</v>
@@ -8728,18 +9423,18 @@
         <v>170.0</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="3" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F171" s="7"/>
-      <c r="G171" s="9" t="s">
-        <v>24</v>
+      <c r="G171" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>35</v>
@@ -8772,11 +9467,11 @@
         <v>20</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="F172" s="7"/>
       <c r="G172" s="9" t="s">
@@ -8810,18 +9505,18 @@
         <v>172.0</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="F173" s="7"/>
-      <c r="G173" s="9" t="s">
-        <v>24</v>
+      <c r="G173" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>15</v>
@@ -8847,14 +9542,26 @@
       <c r="AA173" s="7"/>
     </row>
     <row r="174">
-      <c r="A174" s="2"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="7"/>
+      <c r="A174" s="1">
+        <v>173.0</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
+      <c r="E174" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="F174" s="7"/>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
+      <c r="G174" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I174" s="7"/>
       <c r="J174" s="7"/>
       <c r="K174" s="7"/>
@@ -8876,14 +9583,28 @@
       <c r="AA174" s="7"/>
     </row>
     <row r="175">
-      <c r="A175" s="2"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
+      <c r="A175" s="1">
+        <v>174.0</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="F175" s="7"/>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
+      <c r="G175" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I175" s="7"/>
       <c r="J175" s="7"/>
       <c r="K175" s="7"/>
@@ -8905,14 +9626,26 @@
       <c r="AA175" s="7"/>
     </row>
     <row r="176">
-      <c r="A176" s="2"/>
-      <c r="B176" s="7"/>
-      <c r="C176" s="7"/>
+      <c r="A176" s="1">
+        <v>175.0</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
+      <c r="E176" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="F176" s="7"/>
-      <c r="G176" s="7"/>
-      <c r="H176" s="7"/>
+      <c r="G176" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I176" s="7"/>
       <c r="J176" s="7"/>
       <c r="K176" s="7"/>
@@ -8934,16 +9667,26 @@
       <c r="AA176" s="7"/>
     </row>
     <row r="177">
-      <c r="A177" s="2"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
+      <c r="A177" s="1">
+        <v>176.0</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="D177" s="7"/>
       <c r="E177" s="3" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="F177" s="7"/>
-      <c r="G177" s="7"/>
-      <c r="H177" s="7"/>
+      <c r="G177" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I177" s="7"/>
       <c r="J177" s="7"/>
       <c r="K177" s="7"/>
@@ -8965,14 +9708,26 @@
       <c r="AA177" s="7"/>
     </row>
     <row r="178">
-      <c r="A178" s="2"/>
-      <c r="B178" s="7"/>
-      <c r="C178" s="7"/>
+      <c r="A178" s="1">
+        <v>177.0</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
+      <c r="E178" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="F178" s="7"/>
-      <c r="G178" s="7"/>
-      <c r="H178" s="7"/>
+      <c r="G178" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I178" s="7"/>
       <c r="J178" s="7"/>
       <c r="K178" s="7"/>
@@ -8994,14 +9749,26 @@
       <c r="AA178" s="7"/>
     </row>
     <row r="179">
-      <c r="A179" s="2"/>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
+      <c r="A179" s="1">
+        <v>178.0</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
+      <c r="E179" s="3" t="s">
+        <v>366</v>
+      </c>
       <c r="F179" s="7"/>
-      <c r="G179" s="7"/>
-      <c r="H179" s="7"/>
+      <c r="G179" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I179" s="7"/>
       <c r="J179" s="7"/>
       <c r="K179" s="7"/>
@@ -9023,14 +9790,26 @@
       <c r="AA179" s="7"/>
     </row>
     <row r="180">
-      <c r="A180" s="2"/>
-      <c r="B180" s="7"/>
-      <c r="C180" s="7"/>
+      <c r="A180" s="1">
+        <v>179.0</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
+      <c r="E180" s="3" t="s">
+        <v>368</v>
+      </c>
       <c r="F180" s="7"/>
-      <c r="G180" s="7"/>
-      <c r="H180" s="7"/>
+      <c r="G180" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I180" s="7"/>
       <c r="J180" s="7"/>
       <c r="K180" s="7"/>
@@ -9052,14 +9831,28 @@
       <c r="AA180" s="7"/>
     </row>
     <row r="181">
-      <c r="A181" s="2"/>
-      <c r="B181" s="7"/>
-      <c r="C181" s="7"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
+      <c r="A181" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="F181" s="7"/>
-      <c r="G181" s="7"/>
-      <c r="H181" s="7"/>
+      <c r="G181" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I181" s="7"/>
       <c r="J181" s="7"/>
       <c r="K181" s="7"/>
@@ -9081,14 +9874,28 @@
       <c r="AA181" s="7"/>
     </row>
     <row r="182">
-      <c r="A182" s="2"/>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
+      <c r="A182" s="1">
+        <v>181.0</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="F182" s="7"/>
-      <c r="G182" s="7"/>
-      <c r="H182" s="7"/>
+      <c r="G182" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I182" s="7"/>
       <c r="J182" s="7"/>
       <c r="K182" s="7"/>
@@ -9110,14 +9917,28 @@
       <c r="AA182" s="7"/>
     </row>
     <row r="183">
-      <c r="A183" s="2"/>
-      <c r="B183" s="7"/>
-      <c r="C183" s="7"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
+      <c r="A183" s="1">
+        <v>182.0</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="F183" s="7"/>
-      <c r="G183" s="7"/>
-      <c r="H183" s="7"/>
+      <c r="G183" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I183" s="7"/>
       <c r="J183" s="7"/>
       <c r="K183" s="7"/>
@@ -9139,14 +9960,28 @@
       <c r="AA183" s="7"/>
     </row>
     <row r="184">
-      <c r="A184" s="2"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
+      <c r="A184" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>375</v>
+      </c>
       <c r="F184" s="7"/>
-      <c r="G184" s="7"/>
-      <c r="H184" s="7"/>
+      <c r="G184" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I184" s="7"/>
       <c r="J184" s="7"/>
       <c r="K184" s="7"/>
@@ -9168,14 +10003,28 @@
       <c r="AA184" s="7"/>
     </row>
     <row r="185">
-      <c r="A185" s="2"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
+      <c r="A185" s="1">
+        <v>184.0</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="F185" s="7"/>
-      <c r="G185" s="7"/>
-      <c r="H185" s="7"/>
+      <c r="G185" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I185" s="7"/>
       <c r="J185" s="7"/>
       <c r="K185" s="7"/>
@@ -9197,14 +10046,28 @@
       <c r="AA185" s="7"/>
     </row>
     <row r="186">
-      <c r="A186" s="2"/>
-      <c r="B186" s="7"/>
-      <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
+      <c r="A186" s="1">
+        <v>185.0</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>377</v>
+      </c>
       <c r="F186" s="7"/>
-      <c r="G186" s="7"/>
-      <c r="H186" s="7"/>
+      <c r="G186" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I186" s="7"/>
       <c r="J186" s="7"/>
       <c r="K186" s="7"/>
@@ -9226,14 +10089,28 @@
       <c r="AA186" s="7"/>
     </row>
     <row r="187">
-      <c r="A187" s="2"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
+      <c r="A187" s="1">
+        <v>186.0</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="F187" s="7"/>
-      <c r="G187" s="7"/>
-      <c r="H187" s="7"/>
+      <c r="G187" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I187" s="7"/>
       <c r="J187" s="7"/>
       <c r="K187" s="7"/>
@@ -9255,14 +10132,28 @@
       <c r="AA187" s="7"/>
     </row>
     <row r="188">
-      <c r="A188" s="2"/>
-      <c r="B188" s="7"/>
-      <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
+      <c r="A188" s="1">
+        <v>187.0</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="F188" s="7"/>
-      <c r="G188" s="7"/>
-      <c r="H188" s="7"/>
+      <c r="G188" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
       <c r="K188" s="7"/>
@@ -9284,14 +10175,28 @@
       <c r="AA188" s="7"/>
     </row>
     <row r="189">
-      <c r="A189" s="2"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
+      <c r="A189" s="1">
+        <v>188.0</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="F189" s="7"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
+      <c r="G189" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I189" s="7"/>
       <c r="J189" s="7"/>
       <c r="K189" s="7"/>
@@ -9313,14 +10218,28 @@
       <c r="AA189" s="7"/>
     </row>
     <row r="190">
-      <c r="A190" s="2"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
+      <c r="A190" s="1">
+        <v>189.0</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="F190" s="7"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="7"/>
+      <c r="G190" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I190" s="7"/>
       <c r="J190" s="7"/>
       <c r="K190" s="7"/>
@@ -9342,14 +10261,28 @@
       <c r="AA190" s="7"/>
     </row>
     <row r="191">
-      <c r="A191" s="2"/>
-      <c r="B191" s="7"/>
-      <c r="C191" s="7"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
+      <c r="A191" s="1">
+        <v>190.0</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="F191" s="7"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
+      <c r="G191" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I191" s="7"/>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
@@ -9371,14 +10304,28 @@
       <c r="AA191" s="7"/>
     </row>
     <row r="192">
-      <c r="A192" s="2"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
+      <c r="A192" s="1">
+        <v>191.0</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
+      <c r="G192" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I192" s="7"/>
       <c r="J192" s="7"/>
       <c r="K192" s="7"/>
@@ -9400,14 +10347,28 @@
       <c r="AA192" s="7"/>
     </row>
     <row r="193">
-      <c r="A193" s="2"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
+      <c r="A193" s="1">
+        <v>192.0</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>388</v>
+      </c>
       <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
+      <c r="G193" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I193" s="7"/>
       <c r="J193" s="7"/>
       <c r="K193" s="7"/>
@@ -9429,14 +10390,28 @@
       <c r="AA193" s="7"/>
     </row>
     <row r="194">
-      <c r="A194" s="2"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
+      <c r="A194" s="1">
+        <v>193.0</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>390</v>
+      </c>
       <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
+      <c r="G194" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I194" s="7"/>
       <c r="J194" s="7"/>
       <c r="K194" s="7"/>
@@ -9458,14 +10433,25 @@
       <c r="AA194" s="7"/>
     </row>
     <row r="195">
-      <c r="A195" s="2"/>
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
+      <c r="A195" s="1">
+        <v>194.0</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>392</v>
+      </c>
       <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="7"/>
+      <c r="G195" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H195" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I195" s="7"/>
       <c r="J195" s="7"/>
       <c r="K195" s="7"/>
@@ -9487,14 +10473,28 @@
       <c r="AA195" s="7"/>
     </row>
     <row r="196">
-      <c r="A196" s="2"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
+      <c r="A196" s="1">
+        <v>195.0</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>394</v>
+      </c>
       <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
+      <c r="G196" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I196" s="7"/>
       <c r="J196" s="7"/>
       <c r="K196" s="7"/>
@@ -9516,14 +10516,26 @@
       <c r="AA196" s="7"/>
     </row>
     <row r="197">
-      <c r="A197" s="2"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
+      <c r="A197" s="1">
+        <v>196.0</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
+      <c r="E197" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="F197" s="7"/>
-      <c r="G197" s="7"/>
-      <c r="H197" s="7"/>
+      <c r="G197" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H197" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I197" s="7"/>
       <c r="J197" s="7"/>
       <c r="K197" s="7"/>
@@ -9545,14 +10557,26 @@
       <c r="AA197" s="7"/>
     </row>
     <row r="198">
-      <c r="A198" s="2"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="7"/>
+      <c r="A198" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
+      <c r="E198" s="3" t="s">
+        <v>395</v>
+      </c>
       <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
-      <c r="H198" s="7"/>
+      <c r="G198" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
       <c r="K198" s="7"/>
@@ -9574,14 +10598,26 @@
       <c r="AA198" s="7"/>
     </row>
     <row r="199">
-      <c r="A199" s="2"/>
-      <c r="B199" s="7"/>
-      <c r="C199" s="7"/>
+      <c r="A199" s="1">
+        <v>198.0</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
+      <c r="E199" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="F199" s="7"/>
-      <c r="G199" s="7"/>
-      <c r="H199" s="7"/>
+      <c r="G199" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H199" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I199" s="7"/>
       <c r="J199" s="7"/>
       <c r="K199" s="7"/>
@@ -9603,14 +10639,28 @@
       <c r="AA199" s="7"/>
     </row>
     <row r="200">
-      <c r="A200" s="2"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
+      <c r="A200" s="1">
+        <v>199.0</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>399</v>
+      </c>
       <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="7"/>
+      <c r="G200" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I200" s="7"/>
       <c r="J200" s="7"/>
       <c r="K200" s="7"/>
@@ -9632,14 +10682,28 @@
       <c r="AA200" s="7"/>
     </row>
     <row r="201">
-      <c r="A201" s="2"/>
-      <c r="B201" s="7"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
+      <c r="A201" s="1">
+        <v>200.0</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="7"/>
+      <c r="G201" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H201" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I201" s="7"/>
       <c r="J201" s="7"/>
       <c r="K201" s="7"/>
@@ -9661,14 +10725,26 @@
       <c r="AA201" s="7"/>
     </row>
     <row r="202">
-      <c r="A202" s="2"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
+      <c r="A202" s="1">
+        <v>201.0</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>402</v>
+      </c>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
+      <c r="E202" s="3" t="s">
+        <v>403</v>
+      </c>
       <c r="F202" s="7"/>
-      <c r="G202" s="7"/>
-      <c r="H202" s="7"/>
+      <c r="G202" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H202" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I202" s="7"/>
       <c r="J202" s="7"/>
       <c r="K202" s="7"/>
@@ -9690,14 +10766,28 @@
       <c r="AA202" s="7"/>
     </row>
     <row r="203">
-      <c r="A203" s="2"/>
-      <c r="B203" s="7"/>
-      <c r="C203" s="7"/>
+      <c r="A203" s="1">
+        <v>202.0</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>404</v>
+      </c>
       <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="7"/>
+      <c r="E203" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H203" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
       <c r="K203" s="7"/>
@@ -9719,14 +10809,28 @@
       <c r="AA203" s="7"/>
     </row>
     <row r="204">
-      <c r="A204" s="2"/>
-      <c r="B204" s="7"/>
-      <c r="C204" s="7"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
+      <c r="A204" s="1">
+        <v>203.0</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>409</v>
+      </c>
       <c r="F204" s="7"/>
-      <c r="G204" s="7"/>
-      <c r="H204" s="7"/>
+      <c r="G204" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H204" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I204" s="7"/>
       <c r="J204" s="7"/>
       <c r="K204" s="7"/>
@@ -9748,14 +10852,28 @@
       <c r="AA204" s="7"/>
     </row>
     <row r="205">
-      <c r="A205" s="2"/>
-      <c r="B205" s="7"/>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
+      <c r="A205" s="1">
+        <v>204.0</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>410</v>
+      </c>
       <c r="F205" s="7"/>
-      <c r="G205" s="7"/>
-      <c r="H205" s="7"/>
+      <c r="G205" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H205" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I205" s="7"/>
       <c r="J205" s="7"/>
       <c r="K205" s="7"/>
@@ -9777,14 +10895,28 @@
       <c r="AA205" s="7"/>
     </row>
     <row r="206">
-      <c r="A206" s="2"/>
-      <c r="B206" s="7"/>
-      <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
+      <c r="A206" s="1">
+        <v>205.0</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="F206" s="7"/>
-      <c r="G206" s="7"/>
-      <c r="H206" s="7"/>
+      <c r="G206" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H206" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I206" s="7"/>
       <c r="J206" s="7"/>
       <c r="K206" s="7"/>
@@ -9806,14 +10938,24 @@
       <c r="AA206" s="7"/>
     </row>
     <row r="207">
-      <c r="A207" s="2"/>
-      <c r="B207" s="7"/>
+      <c r="A207" s="1">
+        <v>206.0</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
+      <c r="E207" s="3" t="s">
+        <v>412</v>
+      </c>
       <c r="F207" s="7"/>
-      <c r="G207" s="7"/>
-      <c r="H207" s="7"/>
+      <c r="G207" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H207" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I207" s="7"/>
       <c r="J207" s="7"/>
       <c r="K207" s="7"/>
@@ -9835,14 +10977,28 @@
       <c r="AA207" s="7"/>
     </row>
     <row r="208">
-      <c r="A208" s="2"/>
-      <c r="B208" s="7"/>
-      <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
+      <c r="A208" s="1">
+        <v>207.0</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>413</v>
+      </c>
       <c r="F208" s="7"/>
-      <c r="G208" s="7"/>
-      <c r="H208" s="7"/>
+      <c r="G208" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H208" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I208" s="7"/>
       <c r="J208" s="7"/>
       <c r="K208" s="7"/>
@@ -9864,14 +11020,28 @@
       <c r="AA208" s="7"/>
     </row>
     <row r="209">
-      <c r="A209" s="2"/>
-      <c r="B209" s="7"/>
-      <c r="C209" s="7"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
+      <c r="A209" s="1">
+        <v>208.0</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>414</v>
+      </c>
       <c r="F209" s="7"/>
-      <c r="G209" s="7"/>
-      <c r="H209" s="7"/>
+      <c r="G209" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H209" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I209" s="7"/>
       <c r="J209" s="7"/>
       <c r="K209" s="7"/>
@@ -9893,14 +11063,28 @@
       <c r="AA209" s="7"/>
     </row>
     <row r="210">
-      <c r="A210" s="2"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
+      <c r="A210" s="1">
+        <v>209.0</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>415</v>
+      </c>
       <c r="F210" s="7"/>
-      <c r="G210" s="7"/>
-      <c r="H210" s="7"/>
+      <c r="G210" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H210" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I210" s="7"/>
       <c r="J210" s="7"/>
       <c r="K210" s="7"/>
@@ -9922,14 +11106,28 @@
       <c r="AA210" s="7"/>
     </row>
     <row r="211">
-      <c r="A211" s="2"/>
-      <c r="B211" s="7"/>
-      <c r="C211" s="7"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
+      <c r="A211" s="1">
+        <v>210.0</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>416</v>
+      </c>
       <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
-      <c r="H211" s="7"/>
+      <c r="G211" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H211" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7"/>
       <c r="K211" s="7"/>
@@ -9951,14 +11149,28 @@
       <c r="AA211" s="7"/>
     </row>
     <row r="212">
-      <c r="A212" s="2"/>
-      <c r="B212" s="7"/>
-      <c r="C212" s="7"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
+      <c r="A212" s="1">
+        <v>211.0</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>417</v>
+      </c>
       <c r="F212" s="7"/>
-      <c r="G212" s="7"/>
-      <c r="H212" s="7"/>
+      <c r="G212" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H212" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I212" s="7"/>
       <c r="J212" s="7"/>
       <c r="K212" s="7"/>
@@ -9980,14 +11192,28 @@
       <c r="AA212" s="7"/>
     </row>
     <row r="213">
-      <c r="A213" s="2"/>
-      <c r="B213" s="7"/>
-      <c r="C213" s="7"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
+      <c r="A213" s="1">
+        <v>212.0</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="F213" s="7"/>
-      <c r="G213" s="7"/>
-      <c r="H213" s="7"/>
+      <c r="G213" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H213" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7"/>
       <c r="K213" s="7"/>
@@ -10009,14 +11235,28 @@
       <c r="AA213" s="7"/>
     </row>
     <row r="214">
-      <c r="A214" s="2"/>
-      <c r="B214" s="7"/>
-      <c r="C214" s="7"/>
-      <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
+      <c r="A214" s="1">
+        <v>213.0</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>419</v>
+      </c>
       <c r="F214" s="7"/>
-      <c r="G214" s="7"/>
-      <c r="H214" s="7"/>
+      <c r="G214" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H214" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I214" s="7"/>
       <c r="J214" s="7"/>
       <c r="K214" s="7"/>
@@ -10038,14 +11278,28 @@
       <c r="AA214" s="7"/>
     </row>
     <row r="215">
-      <c r="A215" s="2"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
+      <c r="A215" s="1">
+        <v>214.0</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>420</v>
+      </c>
       <c r="F215" s="7"/>
-      <c r="G215" s="7"/>
-      <c r="H215" s="7"/>
+      <c r="G215" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H215" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I215" s="7"/>
       <c r="J215" s="7"/>
       <c r="K215" s="7"/>
@@ -10067,14 +11321,28 @@
       <c r="AA215" s="7"/>
     </row>
     <row r="216">
-      <c r="A216" s="2"/>
-      <c r="B216" s="7"/>
-      <c r="C216" s="7"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
+      <c r="A216" s="1">
+        <v>215.0</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="F216" s="7"/>
-      <c r="G216" s="7"/>
-      <c r="H216" s="7"/>
+      <c r="G216" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H216" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I216" s="7"/>
       <c r="J216" s="7"/>
       <c r="K216" s="7"/>
@@ -10096,14 +11364,28 @@
       <c r="AA216" s="7"/>
     </row>
     <row r="217">
-      <c r="A217" s="2"/>
-      <c r="B217" s="7"/>
-      <c r="C217" s="7"/>
-      <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
+      <c r="A217" s="1">
+        <v>216.0</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>424</v>
+      </c>
       <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
-      <c r="H217" s="7"/>
+      <c r="G217" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H217" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I217" s="7"/>
       <c r="J217" s="7"/>
       <c r="K217" s="7"/>
@@ -10125,14 +11407,26 @@
       <c r="AA217" s="7"/>
     </row>
     <row r="218">
-      <c r="A218" s="2"/>
-      <c r="B218" s="7"/>
-      <c r="C218" s="7"/>
+      <c r="A218" s="1">
+        <v>217.0</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
+      <c r="E218" s="3" t="s">
+        <v>425</v>
+      </c>
       <c r="F218" s="7"/>
-      <c r="G218" s="7"/>
-      <c r="H218" s="7"/>
+      <c r="G218" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H218" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I218" s="7"/>
       <c r="J218" s="7"/>
       <c r="K218" s="7"/>
@@ -10154,14 +11448,28 @@
       <c r="AA218" s="7"/>
     </row>
     <row r="219">
-      <c r="A219" s="2"/>
-      <c r="B219" s="7"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
+      <c r="A219" s="1">
+        <v>218.0</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>427</v>
+      </c>
       <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
-      <c r="H219" s="7"/>
+      <c r="G219" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H219" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I219" s="7"/>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
@@ -10183,14 +11491,28 @@
       <c r="AA219" s="7"/>
     </row>
     <row r="220">
-      <c r="A220" s="2"/>
-      <c r="B220" s="7"/>
-      <c r="C220" s="7"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="7"/>
+      <c r="A220" s="1">
+        <v>219.0</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="E220" s="11" t="s">
+        <v>430</v>
+      </c>
       <c r="F220" s="7"/>
-      <c r="G220" s="7"/>
-      <c r="H220" s="7"/>
+      <c r="G220" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H220" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
       <c r="K220" s="7"/>
@@ -10212,14 +11534,28 @@
       <c r="AA220" s="7"/>
     </row>
     <row r="221">
-      <c r="A221" s="2"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
+      <c r="A221" s="1">
+        <v>220.0</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
-      <c r="H221" s="7"/>
+      <c r="G221" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H221" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I221" s="7"/>
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
@@ -10241,14 +11577,28 @@
       <c r="AA221" s="7"/>
     </row>
     <row r="222">
-      <c r="A222" s="2"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
+      <c r="A222" s="1">
+        <v>221.0</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>432</v>
+      </c>
       <c r="F222" s="7"/>
-      <c r="G222" s="7"/>
-      <c r="H222" s="7"/>
+      <c r="G222" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H222" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I222" s="7"/>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -10270,14 +11620,28 @@
       <c r="AA222" s="7"/>
     </row>
     <row r="223">
-      <c r="A223" s="2"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="7"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
+      <c r="A223" s="1">
+        <v>222.0</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>435</v>
+      </c>
       <c r="F223" s="7"/>
-      <c r="G223" s="7"/>
-      <c r="H223" s="7"/>
+      <c r="G223" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H223" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I223" s="7"/>
       <c r="J223" s="7"/>
       <c r="K223" s="7"/>
@@ -10299,14 +11663,26 @@
       <c r="AA223" s="7"/>
     </row>
     <row r="224">
-      <c r="A224" s="2"/>
-      <c r="B224" s="7"/>
-      <c r="C224" s="7"/>
+      <c r="A224" s="1">
+        <v>223.0</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>436</v>
+      </c>
       <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
+      <c r="E224" s="3" t="s">
+        <v>437</v>
+      </c>
       <c r="F224" s="7"/>
-      <c r="G224" s="7"/>
-      <c r="H224" s="7"/>
+      <c r="G224" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H224" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I224" s="7"/>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10328,14 +11704,30 @@
       <c r="AA224" s="7"/>
     </row>
     <row r="225">
-      <c r="A225" s="2"/>
-      <c r="B225" s="7"/>
-      <c r="C225" s="7"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
-      <c r="F225" s="7"/>
-      <c r="G225" s="7"/>
-      <c r="H225" s="7"/>
+      <c r="A225" s="1">
+        <v>224.0</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H225" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I225" s="7"/>
       <c r="J225" s="7"/>
       <c r="K225" s="7"/>
@@ -10357,14 +11749,30 @@
       <c r="AA225" s="7"/>
     </row>
     <row r="226">
-      <c r="A226" s="2"/>
-      <c r="B226" s="7"/>
-      <c r="C226" s="7"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="7"/>
-      <c r="G226" s="7"/>
-      <c r="H226" s="7"/>
+      <c r="A226" s="1">
+        <v>225.0</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I226" s="7"/>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10386,14 +11794,26 @@
       <c r="AA226" s="7"/>
     </row>
     <row r="227">
-      <c r="A227" s="2"/>
-      <c r="B227" s="7"/>
-      <c r="C227" s="7"/>
+      <c r="A227" s="1">
+        <v>226.0</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
+      <c r="E227" s="3" t="s">
+        <v>443</v>
+      </c>
       <c r="F227" s="7"/>
-      <c r="G227" s="7"/>
-      <c r="H227" s="7"/>
+      <c r="G227" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H227" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I227" s="7"/>
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
@@ -10415,14 +11835,28 @@
       <c r="AA227" s="7"/>
     </row>
     <row r="228">
-      <c r="A228" s="2"/>
-      <c r="B228" s="7"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
+      <c r="A228" s="1">
+        <v>227.0</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>445</v>
+      </c>
       <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
-      <c r="H228" s="7"/>
+      <c r="G228" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H228" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I228" s="7"/>
       <c r="J228" s="7"/>
       <c r="K228" s="7"/>
@@ -10444,14 +11878,28 @@
       <c r="AA228" s="7"/>
     </row>
     <row r="229">
-      <c r="A229" s="2"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
+      <c r="A229" s="1">
+        <v>228.0</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>446</v>
+      </c>
       <c r="F229" s="7"/>
-      <c r="G229" s="7"/>
-      <c r="H229" s="7"/>
+      <c r="G229" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H229" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I229" s="7"/>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10473,14 +11921,30 @@
       <c r="AA229" s="7"/>
     </row>
     <row r="230">
-      <c r="A230" s="2"/>
-      <c r="B230" s="7"/>
-      <c r="C230" s="7"/>
-      <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
-      <c r="G230" s="7"/>
-      <c r="H230" s="7"/>
+      <c r="A230" s="1">
+        <v>229.0</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="G230" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H230" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I230" s="7"/>
       <c r="J230" s="7"/>
       <c r="K230" s="7"/>
@@ -10502,14 +11966,26 @@
       <c r="AA230" s="7"/>
     </row>
     <row r="231">
-      <c r="A231" s="2"/>
-      <c r="B231" s="7"/>
-      <c r="C231" s="7"/>
+      <c r="A231" s="1">
+        <v>230.0</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
+      <c r="E231" s="3" t="s">
+        <v>449</v>
+      </c>
       <c r="F231" s="7"/>
-      <c r="G231" s="7"/>
-      <c r="H231" s="7"/>
+      <c r="G231" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H231" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I231" s="7"/>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10531,14 +12007,28 @@
       <c r="AA231" s="7"/>
     </row>
     <row r="232">
-      <c r="A232" s="2"/>
-      <c r="B232" s="7"/>
-      <c r="C232" s="7"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
+      <c r="A232" s="1">
+        <v>231.0</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="F232" s="7"/>
-      <c r="G232" s="7"/>
-      <c r="H232" s="7"/>
+      <c r="G232" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H232" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I232" s="7"/>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10560,14 +12050,26 @@
       <c r="AA232" s="7"/>
     </row>
     <row r="233">
-      <c r="A233" s="2"/>
-      <c r="B233" s="7"/>
-      <c r="C233" s="7"/>
+      <c r="A233" s="1">
+        <v>232.0</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
+      <c r="E233" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="F233" s="7"/>
-      <c r="G233" s="7"/>
-      <c r="H233" s="7"/>
+      <c r="G233" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H233" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I233" s="7"/>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
@@ -10589,14 +12091,28 @@
       <c r="AA233" s="7"/>
     </row>
     <row r="234">
-      <c r="A234" s="2"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
+      <c r="A234" s="1">
+        <v>233.0</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>455</v>
+      </c>
       <c r="F234" s="7"/>
-      <c r="G234" s="7"/>
-      <c r="H234" s="7"/>
+      <c r="G234" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H234" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I234" s="7"/>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10618,14 +12134,28 @@
       <c r="AA234" s="7"/>
     </row>
     <row r="235">
-      <c r="A235" s="2"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
-      <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
+      <c r="A235" s="1">
+        <v>234.0</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C235" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="E235" s="11" t="s">
+        <v>457</v>
+      </c>
       <c r="F235" s="7"/>
-      <c r="G235" s="7"/>
-      <c r="H235" s="7"/>
+      <c r="G235" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H235" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I235" s="7"/>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10647,14 +12177,26 @@
       <c r="AA235" s="7"/>
     </row>
     <row r="236">
-      <c r="A236" s="2"/>
-      <c r="B236" s="7"/>
-      <c r="C236" s="7"/>
+      <c r="A236" s="1">
+        <v>235.0</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>444</v>
+      </c>
       <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
+      <c r="E236" s="3" t="s">
+        <v>458</v>
+      </c>
       <c r="F236" s="7"/>
-      <c r="G236" s="7"/>
-      <c r="H236" s="7"/>
+      <c r="G236" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H236" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I236" s="7"/>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10676,15 +12218,27 @@
       <c r="AA236" s="7"/>
     </row>
     <row r="237">
-      <c r="A237" s="2"/>
-      <c r="B237" s="7"/>
+      <c r="A237" s="1">
+        <v>236.0</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
-      <c r="E237" s="7"/>
+      <c r="E237" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="F237" s="7"/>
-      <c r="G237" s="7"/>
-      <c r="H237" s="7"/>
-      <c r="I237" s="7"/>
+      <c r="G237" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H237" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>460</v>
+      </c>
       <c r="J237" s="7"/>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -10705,14 +12259,28 @@
       <c r="AA237" s="7"/>
     </row>
     <row r="238">
-      <c r="A238" s="2"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
+      <c r="A238" s="1">
+        <v>237.0</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>462</v>
+      </c>
       <c r="F238" s="7"/>
-      <c r="G238" s="7"/>
-      <c r="H238" s="7"/>
+      <c r="G238" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H238" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
@@ -10734,14 +12302,28 @@
       <c r="AA238" s="7"/>
     </row>
     <row r="239">
-      <c r="A239" s="2"/>
-      <c r="B239" s="7"/>
-      <c r="C239" s="7"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
+      <c r="A239" s="1">
+        <v>238.0</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>464</v>
+      </c>
       <c r="F239" s="7"/>
-      <c r="G239" s="7"/>
-      <c r="H239" s="7"/>
+      <c r="G239" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H239" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I239" s="7"/>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10763,14 +12345,28 @@
       <c r="AA239" s="7"/>
     </row>
     <row r="240">
-      <c r="A240" s="2"/>
-      <c r="B240" s="7"/>
-      <c r="C240" s="7"/>
+      <c r="A240" s="1">
+        <v>239.0</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>433</v>
+      </c>
       <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
-      <c r="G240" s="7"/>
-      <c r="H240" s="7"/>
+      <c r="E240" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H240" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I240" s="7"/>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10792,14 +12388,30 @@
       <c r="AA240" s="7"/>
     </row>
     <row r="241">
-      <c r="A241" s="2"/>
-      <c r="B241" s="7"/>
-      <c r="C241" s="7"/>
-      <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
-      <c r="F241" s="7"/>
-      <c r="G241" s="7"/>
-      <c r="H241" s="7"/>
+      <c r="A241" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H241" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I241" s="7"/>
       <c r="J241" s="7"/>
       <c r="K241" s="7"/>
@@ -10821,14 +12433,30 @@
       <c r="AA241" s="7"/>
     </row>
     <row r="242">
-      <c r="A242" s="2"/>
-      <c r="B242" s="7"/>
-      <c r="C242" s="7"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
-      <c r="G242" s="7"/>
-      <c r="H242" s="7"/>
+      <c r="A242" s="1">
+        <v>241.0</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H242" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I242" s="7"/>
       <c r="J242" s="7"/>
       <c r="K242" s="7"/>
@@ -10850,14 +12478,28 @@
       <c r="AA242" s="7"/>
     </row>
     <row r="243">
-      <c r="A243" s="2"/>
-      <c r="B243" s="7"/>
-      <c r="C243" s="7"/>
-      <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
+      <c r="A243" s="1">
+        <v>242.0</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>474</v>
+      </c>
       <c r="F243" s="7"/>
-      <c r="G243" s="7"/>
-      <c r="H243" s="7"/>
+      <c r="G243" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H243" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I243" s="7"/>
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
@@ -10879,14 +12521,30 @@
       <c r="AA243" s="7"/>
     </row>
     <row r="244">
-      <c r="A244" s="2"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="7"/>
-      <c r="H244" s="7"/>
+      <c r="A244" s="1">
+        <v>243.0</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G244" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H244" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I244" s="7"/>
       <c r="J244" s="7"/>
       <c r="K244" s="7"/>
@@ -10908,14 +12566,28 @@
       <c r="AA244" s="7"/>
     </row>
     <row r="245">
-      <c r="A245" s="2"/>
-      <c r="B245" s="7"/>
-      <c r="C245" s="7"/>
+      <c r="A245" s="1">
+        <v>244.0</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>472</v>
+      </c>
       <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
-      <c r="G245" s="7"/>
-      <c r="H245" s="7"/>
+      <c r="E245" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H245" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I245" s="7"/>
       <c r="J245" s="7"/>
       <c r="K245" s="7"/>
@@ -10937,14 +12609,28 @@
       <c r="AA245" s="7"/>
     </row>
     <row r="246">
-      <c r="A246" s="2"/>
-      <c r="B246" s="7"/>
-      <c r="C246" s="7"/>
+      <c r="A246" s="1">
+        <v>245.0</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="D246" s="7"/>
-      <c r="E246" s="7"/>
-      <c r="F246" s="7"/>
-      <c r="G246" s="7"/>
-      <c r="H246" s="7"/>
+      <c r="E246" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G246" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H246" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I246" s="7"/>
       <c r="J246" s="7"/>
       <c r="K246" s="7"/>
@@ -10966,15 +12652,29 @@
       <c r="AA246" s="7"/>
     </row>
     <row r="247">
-      <c r="A247" s="2"/>
-      <c r="B247" s="7"/>
-      <c r="C247" s="7"/>
+      <c r="A247" s="1">
+        <v>246.0</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
+      <c r="E247" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="F247" s="7"/>
-      <c r="G247" s="7"/>
-      <c r="H247" s="7"/>
-      <c r="I247" s="7"/>
+      <c r="G247" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H247" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>482</v>
+      </c>
       <c r="J247" s="7"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -10995,14 +12695,28 @@
       <c r="AA247" s="7"/>
     </row>
     <row r="248">
-      <c r="A248" s="2"/>
-      <c r="B248" s="7"/>
-      <c r="C248" s="7"/>
-      <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
+      <c r="A248" s="1">
+        <v>247.0</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>484</v>
+      </c>
       <c r="F248" s="7"/>
-      <c r="G248" s="7"/>
-      <c r="H248" s="7"/>
+      <c r="G248" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H248" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I248" s="7"/>
       <c r="J248" s="7"/>
       <c r="K248" s="7"/>
@@ -11024,14 +12738,28 @@
       <c r="AA248" s="7"/>
     </row>
     <row r="249">
-      <c r="A249" s="2"/>
-      <c r="B249" s="7"/>
-      <c r="C249" s="7"/>
-      <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
+      <c r="A249" s="1">
+        <v>248.0</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>486</v>
+      </c>
       <c r="F249" s="7"/>
-      <c r="G249" s="7"/>
-      <c r="H249" s="7"/>
+      <c r="G249" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H249" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="I249" s="7"/>
       <c r="J249" s="7"/>
       <c r="K249" s="7"/>
@@ -11053,14 +12781,28 @@
       <c r="AA249" s="7"/>
     </row>
     <row r="250">
-      <c r="A250" s="2"/>
-      <c r="B250" s="7"/>
-      <c r="C250" s="7"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="7"/>
+      <c r="A250" s="1">
+        <v>249.0</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>487</v>
+      </c>
       <c r="F250" s="7"/>
-      <c r="G250" s="7"/>
-      <c r="H250" s="7"/>
+      <c r="G250" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H250" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I250" s="7"/>
       <c r="J250" s="7"/>
       <c r="K250" s="7"/>
@@ -11082,14 +12824,28 @@
       <c r="AA250" s="7"/>
     </row>
     <row r="251">
-      <c r="A251" s="2"/>
-      <c r="B251" s="7"/>
-      <c r="C251" s="7"/>
-      <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
+      <c r="A251" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>489</v>
+      </c>
       <c r="F251" s="7"/>
-      <c r="G251" s="7"/>
-      <c r="H251" s="7"/>
+      <c r="G251" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H251" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I251" s="7"/>
       <c r="J251" s="7"/>
       <c r="K251" s="7"/>
@@ -11111,14 +12867,26 @@
       <c r="AA251" s="7"/>
     </row>
     <row r="252">
-      <c r="A252" s="2"/>
-      <c r="B252" s="7"/>
-      <c r="C252" s="7"/>
-      <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
+      <c r="A252" s="1">
+        <v>251.0</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D252" s="3"/>
+      <c r="E252" s="3" t="s">
+        <v>491</v>
+      </c>
       <c r="F252" s="7"/>
-      <c r="G252" s="7"/>
-      <c r="H252" s="7"/>
+      <c r="G252" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H252" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I252" s="7"/>
       <c r="J252" s="7"/>
       <c r="K252" s="7"/>
@@ -11140,14 +12908,28 @@
       <c r="AA252" s="7"/>
     </row>
     <row r="253">
-      <c r="A253" s="2"/>
-      <c r="B253" s="7"/>
-      <c r="C253" s="7"/>
-      <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
+      <c r="A253" s="1">
+        <v>252.0</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>493</v>
+      </c>
       <c r="F253" s="7"/>
-      <c r="G253" s="7"/>
-      <c r="H253" s="7"/>
+      <c r="G253" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H253" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I253" s="7"/>
       <c r="J253" s="7"/>
       <c r="K253" s="7"/>
@@ -11169,14 +12951,28 @@
       <c r="AA253" s="7"/>
     </row>
     <row r="254">
-      <c r="A254" s="2"/>
-      <c r="B254" s="7"/>
-      <c r="C254" s="7"/>
-      <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
+      <c r="A254" s="1">
+        <v>253.0</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>494</v>
+      </c>
       <c r="F254" s="7"/>
-      <c r="G254" s="7"/>
-      <c r="H254" s="7"/>
+      <c r="G254" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H254" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I254" s="7"/>
       <c r="J254" s="7"/>
       <c r="K254" s="7"/>
@@ -11198,14 +12994,28 @@
       <c r="AA254" s="7"/>
     </row>
     <row r="255">
-      <c r="A255" s="2"/>
-      <c r="B255" s="7"/>
-      <c r="C255" s="7"/>
-      <c r="D255" s="7"/>
-      <c r="E255" s="7"/>
+      <c r="A255" s="1">
+        <v>254.0</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>495</v>
+      </c>
       <c r="F255" s="7"/>
-      <c r="G255" s="7"/>
-      <c r="H255" s="7"/>
+      <c r="G255" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H255" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I255" s="7"/>
       <c r="J255" s="7"/>
       <c r="K255" s="7"/>
@@ -11227,14 +13037,28 @@
       <c r="AA255" s="7"/>
     </row>
     <row r="256">
-      <c r="A256" s="2"/>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
-      <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
+      <c r="A256" s="1">
+        <v>255.0</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>496</v>
+      </c>
       <c r="F256" s="7"/>
-      <c r="G256" s="7"/>
-      <c r="H256" s="7"/>
+      <c r="G256" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H256" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I256" s="7"/>
       <c r="J256" s="7"/>
       <c r="K256" s="7"/>
@@ -11256,14 +13080,28 @@
       <c r="AA256" s="7"/>
     </row>
     <row r="257">
-      <c r="A257" s="2"/>
-      <c r="B257" s="7"/>
-      <c r="C257" s="7"/>
-      <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
+      <c r="A257" s="1">
+        <v>256.0</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="F257" s="7"/>
-      <c r="G257" s="7"/>
-      <c r="H257" s="7"/>
+      <c r="G257" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H257" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I257" s="7"/>
       <c r="J257" s="7"/>
       <c r="K257" s="7"/>
@@ -11285,14 +13123,28 @@
       <c r="AA257" s="7"/>
     </row>
     <row r="258">
-      <c r="A258" s="2"/>
-      <c r="B258" s="7"/>
-      <c r="C258" s="7"/>
+      <c r="A258" s="1">
+        <v>257.0</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-      <c r="G258" s="7"/>
-      <c r="H258" s="7"/>
+      <c r="E258" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G258" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H258" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I258" s="7"/>
       <c r="J258" s="7"/>
       <c r="K258" s="7"/>
@@ -11314,14 +13166,28 @@
       <c r="AA258" s="7"/>
     </row>
     <row r="259">
-      <c r="A259" s="2"/>
-      <c r="B259" s="7"/>
-      <c r="C259" s="7"/>
-      <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
+      <c r="A259" s="1">
+        <v>258.0</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="F259" s="7"/>
-      <c r="G259" s="7"/>
-      <c r="H259" s="7"/>
+      <c r="G259" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H259" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I259" s="7"/>
       <c r="J259" s="7"/>
       <c r="K259" s="7"/>
@@ -11343,14 +13209,28 @@
       <c r="AA259" s="7"/>
     </row>
     <row r="260">
-      <c r="A260" s="2"/>
-      <c r="B260" s="7"/>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
+      <c r="A260" s="1">
+        <v>259.0</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="F260" s="7"/>
-      <c r="G260" s="7"/>
-      <c r="H260" s="7"/>
+      <c r="G260" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H260" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I260" s="7"/>
       <c r="J260" s="7"/>
       <c r="K260" s="7"/>
@@ -11372,14 +13252,28 @@
       <c r="AA260" s="7"/>
     </row>
     <row r="261">
-      <c r="A261" s="2"/>
-      <c r="B261" s="7"/>
-      <c r="C261" s="7"/>
-      <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
+      <c r="A261" s="1">
+        <v>260.0</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="F261" s="7"/>
-      <c r="G261" s="7"/>
-      <c r="H261" s="7"/>
+      <c r="G261" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H261" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I261" s="7"/>
       <c r="J261" s="7"/>
       <c r="K261" s="7"/>
@@ -11401,14 +13295,26 @@
       <c r="AA261" s="7"/>
     </row>
     <row r="262">
-      <c r="A262" s="2"/>
-      <c r="B262" s="7"/>
-      <c r="C262" s="7"/>
+      <c r="A262" s="1">
+        <v>261.0</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
+      <c r="E262" s="3" t="s">
+        <v>506</v>
+      </c>
       <c r="F262" s="7"/>
-      <c r="G262" s="7"/>
-      <c r="H262" s="7"/>
+      <c r="G262" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H262" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I262" s="7"/>
       <c r="J262" s="7"/>
       <c r="K262" s="7"/>
@@ -11430,14 +13336,26 @@
       <c r="AA262" s="7"/>
     </row>
     <row r="263">
-      <c r="A263" s="2"/>
-      <c r="B263" s="7"/>
-      <c r="C263" s="7"/>
+      <c r="A263" s="1">
+        <v>262.0</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="D263" s="7"/>
-      <c r="E263" s="7"/>
+      <c r="E263" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F263" s="7"/>
-      <c r="G263" s="7"/>
-      <c r="H263" s="7"/>
+      <c r="G263" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H263" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I263" s="7"/>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11459,14 +13377,26 @@
       <c r="AA263" s="7"/>
     </row>
     <row r="264">
-      <c r="A264" s="2"/>
-      <c r="B264" s="7"/>
-      <c r="C264" s="7"/>
+      <c r="A264" s="1">
+        <v>263.0</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>488</v>
+      </c>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
+      <c r="E264" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="F264" s="7"/>
-      <c r="G264" s="7"/>
-      <c r="H264" s="7"/>
+      <c r="G264" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H264" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I264" s="7"/>
       <c r="J264" s="7"/>
       <c r="K264" s="7"/>
@@ -11488,14 +13418,28 @@
       <c r="AA264" s="7"/>
     </row>
     <row r="265">
-      <c r="A265" s="2"/>
-      <c r="B265" s="7"/>
-      <c r="C265" s="7"/>
-      <c r="D265" s="7"/>
-      <c r="E265" s="7"/>
+      <c r="A265" s="1">
+        <v>264.0</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="F265" s="7"/>
-      <c r="G265" s="7"/>
-      <c r="H265" s="7"/>
+      <c r="G265" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H265" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I265" s="7"/>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
@@ -11517,14 +13461,30 @@
       <c r="AA265" s="7"/>
     </row>
     <row r="266">
-      <c r="A266" s="2"/>
-      <c r="B266" s="7"/>
-      <c r="C266" s="7"/>
-      <c r="D266" s="7"/>
-      <c r="E266" s="7"/>
-      <c r="F266" s="7"/>
-      <c r="G266" s="7"/>
-      <c r="H266" s="7"/>
+      <c r="A266" s="1">
+        <v>265.0</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H266" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
@@ -11546,14 +13506,26 @@
       <c r="AA266" s="7"/>
     </row>
     <row r="267">
-      <c r="A267" s="2"/>
-      <c r="B267" s="7"/>
-      <c r="C267" s="7"/>
+      <c r="A267" s="1">
+        <v>266.0</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
+      <c r="E267" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="F267" s="7"/>
-      <c r="G267" s="7"/>
-      <c r="H267" s="7"/>
+      <c r="G267" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H267" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
@@ -11575,14 +13547,30 @@
       <c r="AA267" s="7"/>
     </row>
     <row r="268">
-      <c r="A268" s="2"/>
-      <c r="B268" s="7"/>
-      <c r="C268" s="7"/>
-      <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-      <c r="G268" s="7"/>
-      <c r="H268" s="7"/>
+      <c r="A268" s="1">
+        <v>267.0</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H268" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
       <c r="K268" s="7"/>
@@ -11604,14 +13592,28 @@
       <c r="AA268" s="7"/>
     </row>
     <row r="269">
-      <c r="A269" s="2"/>
-      <c r="B269" s="7"/>
-      <c r="C269" s="7"/>
-      <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
+      <c r="A269" s="1">
+        <v>268.0</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>518</v>
+      </c>
       <c r="F269" s="7"/>
-      <c r="G269" s="7"/>
-      <c r="H269" s="7"/>
+      <c r="G269" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H269" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I269" s="7"/>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11633,14 +13635,26 @@
       <c r="AA269" s="7"/>
     </row>
     <row r="270">
-      <c r="A270" s="2"/>
-      <c r="B270" s="7"/>
-      <c r="C270" s="7"/>
+      <c r="A270" s="1">
+        <v>269.0</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="D270" s="7"/>
-      <c r="E270" s="7"/>
+      <c r="E270" s="3" t="s">
+        <v>519</v>
+      </c>
       <c r="F270" s="7"/>
-      <c r="G270" s="7"/>
-      <c r="H270" s="7"/>
+      <c r="G270" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H270" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I270" s="7"/>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11662,14 +13676,28 @@
       <c r="AA270" s="7"/>
     </row>
     <row r="271">
-      <c r="A271" s="2"/>
-      <c r="B271" s="7"/>
-      <c r="C271" s="7"/>
-      <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
+      <c r="A271" s="1">
+        <v>270.0</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="F271" s="7"/>
-      <c r="G271" s="7"/>
-      <c r="H271" s="7"/>
+      <c r="G271" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H271" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I271" s="7"/>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11691,14 +13719,28 @@
       <c r="AA271" s="7"/>
     </row>
     <row r="272">
-      <c r="A272" s="2"/>
-      <c r="B272" s="7"/>
-      <c r="C272" s="7"/>
-      <c r="D272" s="7"/>
-      <c r="E272" s="7"/>
+      <c r="A272" s="1">
+        <v>271.0</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>521</v>
+      </c>
       <c r="F272" s="7"/>
-      <c r="G272" s="7"/>
-      <c r="H272" s="7"/>
+      <c r="G272" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H272" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I272" s="7"/>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11720,14 +13762,28 @@
       <c r="AA272" s="7"/>
     </row>
     <row r="273">
-      <c r="A273" s="2"/>
-      <c r="B273" s="7"/>
-      <c r="C273" s="7"/>
-      <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
+      <c r="A273" s="1">
+        <v>272.0</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>522</v>
+      </c>
       <c r="F273" s="7"/>
-      <c r="G273" s="7"/>
-      <c r="H273" s="7"/>
+      <c r="G273" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H273" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I273" s="7"/>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11749,14 +13805,28 @@
       <c r="AA273" s="7"/>
     </row>
     <row r="274">
-      <c r="A274" s="2"/>
-      <c r="B274" s="7"/>
-      <c r="C274" s="7"/>
-      <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
+      <c r="A274" s="1">
+        <v>273.0</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>523</v>
+      </c>
       <c r="F274" s="7"/>
-      <c r="G274" s="7"/>
-      <c r="H274" s="7"/>
+      <c r="G274" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H274" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I274" s="7"/>
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
@@ -11778,14 +13848,30 @@
       <c r="AA274" s="7"/>
     </row>
     <row r="275">
-      <c r="A275" s="2"/>
-      <c r="B275" s="7"/>
-      <c r="C275" s="7"/>
-      <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
-      <c r="G275" s="7"/>
-      <c r="H275" s="7"/>
+      <c r="A275" s="1">
+        <v>274.0</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H275" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I275" s="7"/>
       <c r="J275" s="7"/>
       <c r="K275" s="7"/>
@@ -11807,14 +13893,26 @@
       <c r="AA275" s="7"/>
     </row>
     <row r="276">
-      <c r="A276" s="2"/>
-      <c r="B276" s="7"/>
-      <c r="C276" s="7"/>
+      <c r="A276" s="1">
+        <v>275.0</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>526</v>
+      </c>
       <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
+      <c r="E276" s="3" t="s">
+        <v>527</v>
+      </c>
       <c r="F276" s="7"/>
-      <c r="G276" s="7"/>
-      <c r="H276" s="7"/>
+      <c r="G276" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H276" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I276" s="7"/>
       <c r="J276" s="7"/>
       <c r="K276" s="7"/>
@@ -11836,15 +13934,27 @@
       <c r="AA276" s="7"/>
     </row>
     <row r="277">
-      <c r="A277" s="2"/>
-      <c r="B277" s="7"/>
+      <c r="A277" s="1">
+        <v>276.0</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
+      <c r="E277" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="F277" s="7"/>
-      <c r="G277" s="7"/>
-      <c r="H277" s="7"/>
-      <c r="I277" s="7"/>
+      <c r="G277" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H277" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>529</v>
+      </c>
       <c r="J277" s="7"/>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -11865,14 +13975,28 @@
       <c r="AA277" s="7"/>
     </row>
     <row r="278">
-      <c r="A278" s="2"/>
-      <c r="B278" s="7"/>
-      <c r="C278" s="7"/>
-      <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
+      <c r="A278" s="1">
+        <v>277.0</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>530</v>
+      </c>
       <c r="F278" s="7"/>
-      <c r="G278" s="7"/>
-      <c r="H278" s="7"/>
+      <c r="G278" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H278" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I278" s="7"/>
       <c r="J278" s="7"/>
       <c r="K278" s="7"/>
@@ -11894,14 +14018,28 @@
       <c r="AA278" s="7"/>
     </row>
     <row r="279">
-      <c r="A279" s="2"/>
-      <c r="B279" s="7"/>
-      <c r="C279" s="7"/>
-      <c r="D279" s="7"/>
-      <c r="E279" s="7"/>
+      <c r="A279" s="1">
+        <v>278.0</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>533</v>
+      </c>
       <c r="F279" s="7"/>
-      <c r="G279" s="7"/>
-      <c r="H279" s="7"/>
+      <c r="G279" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H279" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I279" s="7"/>
       <c r="J279" s="7"/>
       <c r="K279" s="7"/>
@@ -11923,14 +14061,30 @@
       <c r="AA279" s="7"/>
     </row>
     <row r="280">
-      <c r="A280" s="2"/>
-      <c r="B280" s="7"/>
-      <c r="C280" s="7"/>
-      <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
-      <c r="F280" s="7"/>
-      <c r="G280" s="7"/>
-      <c r="H280" s="7"/>
+      <c r="A280" s="1">
+        <v>279.0</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="G280" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H280" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I280" s="7"/>
       <c r="J280" s="7"/>
       <c r="K280" s="7"/>
@@ -11952,14 +14106,28 @@
       <c r="AA280" s="7"/>
     </row>
     <row r="281">
-      <c r="A281" s="2"/>
-      <c r="B281" s="7"/>
-      <c r="C281" s="7"/>
-      <c r="D281" s="7"/>
-      <c r="E281" s="7"/>
+      <c r="A281" s="1">
+        <v>280.0</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="F281" s="7"/>
-      <c r="G281" s="7"/>
-      <c r="H281" s="7"/>
+      <c r="G281" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H281" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I281" s="7"/>
       <c r="J281" s="7"/>
       <c r="K281" s="7"/>
@@ -11981,14 +14149,28 @@
       <c r="AA281" s="7"/>
     </row>
     <row r="282">
-      <c r="A282" s="2"/>
-      <c r="B282" s="7"/>
-      <c r="C282" s="7"/>
-      <c r="D282" s="7"/>
-      <c r="E282" s="7"/>
+      <c r="A282" s="1">
+        <v>281.0</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>538</v>
+      </c>
       <c r="F282" s="7"/>
-      <c r="G282" s="7"/>
-      <c r="H282" s="7"/>
+      <c r="G282" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H282" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I282" s="7"/>
       <c r="J282" s="7"/>
       <c r="K282" s="7"/>
@@ -12010,19 +14192,37 @@
       <c r="AA282" s="7"/>
     </row>
     <row r="283">
-      <c r="A283" s="2"/>
-      <c r="B283" s="7"/>
-      <c r="C283" s="7"/>
-      <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
-      <c r="G283" s="7"/>
-      <c r="H283" s="7"/>
+      <c r="A283" s="1">
+        <v>282.0</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H283" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I283" s="7"/>
       <c r="J283" s="7"/>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c r="M283" s="3" t="s">
+        <v>542</v>
+      </c>
       <c r="N283" s="7"/>
       <c r="O283" s="7"/>
       <c r="P283" s="7"/>
@@ -12039,14 +14239,30 @@
       <c r="AA283" s="7"/>
     </row>
     <row r="284">
-      <c r="A284" s="2"/>
-      <c r="B284" s="7"/>
-      <c r="C284" s="7"/>
-      <c r="D284" s="7"/>
-      <c r="E284" s="7"/>
-      <c r="F284" s="7"/>
-      <c r="G284" s="7"/>
-      <c r="H284" s="7"/>
+      <c r="A284" s="1">
+        <v>283.0</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G284" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I284" s="7"/>
       <c r="J284" s="7"/>
       <c r="K284" s="7"/>
@@ -12068,14 +14284,28 @@
       <c r="AA284" s="7"/>
     </row>
     <row r="285">
-      <c r="A285" s="2"/>
-      <c r="B285" s="7"/>
-      <c r="C285" s="7"/>
-      <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
+      <c r="A285" s="1">
+        <v>284.0</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>546</v>
+      </c>
       <c r="F285" s="7"/>
-      <c r="G285" s="7"/>
-      <c r="H285" s="7"/>
+      <c r="G285" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H285" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I285" s="7"/>
       <c r="J285" s="7"/>
       <c r="K285" s="7"/>
@@ -12097,14 +14327,28 @@
       <c r="AA285" s="7"/>
     </row>
     <row r="286">
-      <c r="A286" s="2"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
-      <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
+      <c r="A286" s="1">
+        <v>285.0</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>548</v>
+      </c>
       <c r="F286" s="7"/>
-      <c r="G286" s="7"/>
-      <c r="H286" s="7"/>
+      <c r="G286" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I286" s="7"/>
       <c r="J286" s="7"/>
       <c r="K286" s="7"/>
@@ -12126,14 +14370,28 @@
       <c r="AA286" s="7"/>
     </row>
     <row r="287">
-      <c r="A287" s="2"/>
-      <c r="B287" s="7"/>
-      <c r="C287" s="7"/>
-      <c r="D287" s="7"/>
-      <c r="E287" s="7"/>
+      <c r="A287" s="1">
+        <v>286.0</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>549</v>
+      </c>
       <c r="F287" s="7"/>
-      <c r="G287" s="7"/>
-      <c r="H287" s="7"/>
+      <c r="G287" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H287" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I287" s="7"/>
       <c r="J287" s="7"/>
       <c r="K287" s="7"/>
@@ -12155,14 +14413,28 @@
       <c r="AA287" s="7"/>
     </row>
     <row r="288">
-      <c r="A288" s="2"/>
-      <c r="B288" s="7"/>
-      <c r="C288" s="7"/>
-      <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
+      <c r="A288" s="1">
+        <v>287.0</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>551</v>
+      </c>
       <c r="F288" s="7"/>
-      <c r="G288" s="7"/>
-      <c r="H288" s="7"/>
+      <c r="G288" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H288" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I288" s="7"/>
       <c r="J288" s="7"/>
       <c r="K288" s="7"/>
@@ -12184,14 +14456,28 @@
       <c r="AA288" s="7"/>
     </row>
     <row r="289">
-      <c r="A289" s="2"/>
-      <c r="B289" s="7"/>
-      <c r="C289" s="7"/>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
+      <c r="A289" s="1">
+        <v>288.0</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>552</v>
+      </c>
       <c r="F289" s="7"/>
-      <c r="G289" s="7"/>
-      <c r="H289" s="7"/>
+      <c r="G289" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H289" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I289" s="7"/>
       <c r="J289" s="7"/>
       <c r="K289" s="7"/>
@@ -12213,14 +14499,28 @@
       <c r="AA289" s="7"/>
     </row>
     <row r="290">
-      <c r="A290" s="2"/>
-      <c r="B290" s="7"/>
-      <c r="C290" s="7"/>
+      <c r="A290" s="1">
+        <v>289.0</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>553</v>
+      </c>
       <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
-      <c r="F290" s="7"/>
-      <c r="G290" s="7"/>
-      <c r="H290" s="7"/>
+      <c r="E290" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G290" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I290" s="7"/>
       <c r="J290" s="7"/>
       <c r="K290" s="7"/>
@@ -12242,14 +14542,28 @@
       <c r="AA290" s="7"/>
     </row>
     <row r="291">
-      <c r="A291" s="2"/>
-      <c r="B291" s="7"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
+      <c r="A291" s="1">
+        <v>290.0</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>557</v>
+      </c>
       <c r="F291" s="7"/>
-      <c r="G291" s="7"/>
-      <c r="H291" s="7"/>
+      <c r="G291" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H291" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I291" s="7"/>
       <c r="J291" s="7"/>
       <c r="K291" s="7"/>
@@ -12271,14 +14585,28 @@
       <c r="AA291" s="7"/>
     </row>
     <row r="292">
-      <c r="A292" s="2"/>
-      <c r="B292" s="7"/>
-      <c r="C292" s="7"/>
-      <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
+      <c r="A292" s="1">
+        <v>291.0</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>559</v>
+      </c>
       <c r="F292" s="7"/>
-      <c r="G292" s="7"/>
-      <c r="H292" s="7"/>
+      <c r="G292" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I292" s="7"/>
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
@@ -12300,14 +14628,28 @@
       <c r="AA292" s="7"/>
     </row>
     <row r="293">
-      <c r="A293" s="2"/>
-      <c r="B293" s="7"/>
-      <c r="C293" s="7"/>
-      <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
+      <c r="A293" s="1">
+        <v>292.0</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>560</v>
+      </c>
       <c r="F293" s="7"/>
-      <c r="G293" s="7"/>
-      <c r="H293" s="7"/>
+      <c r="G293" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H293" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I293" s="7"/>
       <c r="J293" s="7"/>
       <c r="K293" s="7"/>
@@ -12329,14 +14671,26 @@
       <c r="AA293" s="7"/>
     </row>
     <row r="294">
-      <c r="A294" s="2"/>
-      <c r="B294" s="7"/>
-      <c r="C294" s="7"/>
+      <c r="A294" s="1">
+        <v>293.0</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="D294" s="7"/>
-      <c r="E294" s="7"/>
+      <c r="E294" s="3" t="s">
+        <v>561</v>
+      </c>
       <c r="F294" s="7"/>
-      <c r="G294" s="7"/>
-      <c r="H294" s="7"/>
+      <c r="G294" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H294" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I294" s="7"/>
       <c r="J294" s="7"/>
       <c r="K294" s="7"/>
@@ -12358,14 +14712,28 @@
       <c r="AA294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="2"/>
-      <c r="B295" s="7"/>
-      <c r="C295" s="7"/>
-      <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
+      <c r="A295" s="1">
+        <v>294.0</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="F295" s="7"/>
-      <c r="G295" s="7"/>
-      <c r="H295" s="7"/>
+      <c r="G295" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H295" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I295" s="7"/>
       <c r="J295" s="7"/>
       <c r="K295" s="7"/>
@@ -12387,14 +14755,24 @@
       <c r="AA295" s="7"/>
     </row>
     <row r="296">
-      <c r="A296" s="2"/>
-      <c r="B296" s="7"/>
+      <c r="A296" s="1">
+        <v>295.0</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
+      <c r="E296" s="3" t="s">
+        <v>564</v>
+      </c>
       <c r="F296" s="7"/>
-      <c r="G296" s="7"/>
-      <c r="H296" s="7"/>
+      <c r="G296" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H296" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I296" s="7"/>
       <c r="J296" s="7"/>
       <c r="K296" s="7"/>
@@ -12416,14 +14794,28 @@
       <c r="AA296" s="7"/>
     </row>
     <row r="297">
-      <c r="A297" s="2"/>
-      <c r="B297" s="7"/>
-      <c r="C297" s="7"/>
-      <c r="D297" s="7"/>
-      <c r="E297" s="7"/>
+      <c r="A297" s="1">
+        <v>296.0</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>565</v>
+      </c>
       <c r="F297" s="7"/>
-      <c r="G297" s="7"/>
-      <c r="H297" s="7"/>
+      <c r="G297" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H297" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I297" s="7"/>
       <c r="J297" s="7"/>
       <c r="K297" s="7"/>
@@ -12445,14 +14837,21 @@
       <c r="AA297" s="7"/>
     </row>
     <row r="298">
-      <c r="A298" s="2"/>
-      <c r="B298" s="7"/>
-      <c r="C298" s="7"/>
+      <c r="A298" s="1">
+        <v>297.0</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
-      <c r="G298" s="7"/>
-      <c r="H298" s="7"/>
+      <c r="G298" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H298" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I298" s="7"/>
       <c r="J298" s="7"/>
       <c r="K298" s="7"/>
@@ -12474,14 +14873,20 @@
       <c r="AA298" s="7"/>
     </row>
     <row r="299">
-      <c r="A299" s="2"/>
+      <c r="A299" s="1">
+        <v>298.0</v>
+      </c>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
-      <c r="G299" s="7"/>
-      <c r="H299" s="7"/>
+      <c r="G299" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H299" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I299" s="7"/>
       <c r="J299" s="7"/>
       <c r="K299" s="7"/>
@@ -12503,14 +14908,20 @@
       <c r="AA299" s="7"/>
     </row>
     <row r="300">
-      <c r="A300" s="2"/>
+      <c r="A300" s="1">
+        <v>299.0</v>
+      </c>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
-      <c r="G300" s="7"/>
-      <c r="H300" s="7"/>
+      <c r="G300" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H300" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I300" s="7"/>
       <c r="J300" s="7"/>
       <c r="K300" s="7"/>
@@ -12532,14 +14943,20 @@
       <c r="AA300" s="7"/>
     </row>
     <row r="301">
-      <c r="A301" s="2"/>
+      <c r="A301" s="1">
+        <v>300.0</v>
+      </c>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
-      <c r="G301" s="7"/>
-      <c r="H301" s="7"/>
+      <c r="G301" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H301" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I301" s="7"/>
       <c r="J301" s="7"/>
       <c r="K301" s="7"/>
@@ -32833,40 +35250,59 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B173">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B298">
       <formula1>"user,seller,delivery,admin,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H173">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H301">
       <formula1>"critical ,high,medium,low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G173">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G301">
       <formula1>"New,Resolved,Reopen,Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
     <hyperlink r:id="rId2" ref="F9"/>
-    <hyperlink r:id="rId3" ref="F33"/>
-    <hyperlink r:id="rId4" ref="F35"/>
-    <hyperlink r:id="rId5" ref="F43"/>
-    <hyperlink r:id="rId6" ref="F52"/>
-    <hyperlink r:id="rId7" ref="F56"/>
-    <hyperlink r:id="rId8" ref="F64"/>
-    <hyperlink r:id="rId9" ref="F65"/>
-    <hyperlink r:id="rId10" ref="F77"/>
-    <hyperlink r:id="rId11" ref="F85"/>
-    <hyperlink r:id="rId12" ref="F94"/>
-    <hyperlink r:id="rId13" ref="F95"/>
-    <hyperlink r:id="rId14" ref="F96"/>
-    <hyperlink r:id="rId15" ref="F110"/>
-    <hyperlink r:id="rId16" ref="F136"/>
-    <hyperlink r:id="rId17" ref="F142"/>
-    <hyperlink r:id="rId18" ref="F166"/>
-    <hyperlink r:id="rId19" ref="F170"/>
+    <hyperlink r:id="rId3" ref="F17"/>
+    <hyperlink r:id="rId4" ref="F33"/>
+    <hyperlink r:id="rId5" ref="F35"/>
+    <hyperlink r:id="rId6" ref="F43"/>
+    <hyperlink r:id="rId7" ref="F52"/>
+    <hyperlink r:id="rId8" ref="F56"/>
+    <hyperlink r:id="rId9" ref="F64"/>
+    <hyperlink r:id="rId10" ref="F65"/>
+    <hyperlink r:id="rId11" ref="F77"/>
+    <hyperlink r:id="rId12" ref="F85"/>
+    <hyperlink r:id="rId13" ref="F94"/>
+    <hyperlink r:id="rId14" ref="F95"/>
+    <hyperlink r:id="rId15" ref="F96"/>
+    <hyperlink r:id="rId16" ref="F110"/>
+    <hyperlink r:id="rId17" ref="F136"/>
+    <hyperlink r:id="rId18" ref="F142"/>
+    <hyperlink r:id="rId19" ref="F166"/>
+    <hyperlink r:id="rId20" ref="F170"/>
+    <hyperlink r:id="rId21" ref="F203"/>
+    <hyperlink r:id="rId22" ref="F225"/>
+    <hyperlink r:id="rId23" ref="F226"/>
+    <hyperlink r:id="rId24" ref="F230"/>
+    <hyperlink r:id="rId25" ref="F240"/>
+    <hyperlink r:id="rId26" ref="F241"/>
+    <hyperlink r:id="rId27" ref="F242"/>
+    <hyperlink r:id="rId28" ref="F244"/>
+    <hyperlink r:id="rId29" ref="F245"/>
+    <hyperlink r:id="rId30" ref="F246"/>
+    <hyperlink r:id="rId31" ref="F258"/>
+    <hyperlink r:id="rId32" ref="F266"/>
+    <hyperlink r:id="rId33" ref="F268"/>
+    <hyperlink r:id="rId34" ref="F275"/>
+    <hyperlink r:id="rId35" ref="F280"/>
+    <hyperlink r:id="rId36" ref="F283"/>
+    <hyperlink r:id="rId37" ref="F284"/>
+    <hyperlink r:id="rId38" ref="F290"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
+  <drawing r:id="rId39"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId41"/>
   </tableParts>
 </worksheet>
 </file>